--- a/Danh_sach_dai_ly_toa_do_Final.xlsx
+++ b/Danh_sach_dai_ly_toa_do_Final.xlsx
@@ -55,7 +55,7 @@
     <t>Đồng Tháp</t>
   </si>
   <si>
-    <t>Bạc liêu-ST-CM</t>
+    <t>Bạc Liêu-ST-CM</t>
   </si>
   <si>
     <t>An Giang</t>

--- a/Danh_sach_dai_ly_toa_do_Final.xlsx
+++ b/Danh_sach_dai_ly_toa_do_Final.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mapDaiLyPhuNong\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF5C4FB-328B-4509-BA41-54742562AC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -3580,8 +3586,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3644,13 +3650,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3688,7 +3702,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3722,6 +3736,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3756,9 +3771,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3931,11 +3947,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E639"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3952,7 +3972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -3963,13 +3983,13 @@
         <v>106.711</v>
       </c>
       <c r="D2">
-        <v>10.4379</v>
+        <v>10.437900000000001</v>
       </c>
       <c r="E2" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3986,7 +4006,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3994,16 +4014,16 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>106.674</v>
+        <v>106.67400000000001</v>
       </c>
       <c r="D4">
-        <v>10.3624</v>
+        <v>10.362399999999999</v>
       </c>
       <c r="E4" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -4011,16 +4031,16 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>106.716</v>
+        <v>106.71599999999999</v>
       </c>
       <c r="D5">
-        <v>10.4014</v>
+        <v>10.401400000000001</v>
       </c>
       <c r="E5" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4037,7 +4057,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -4054,7 +4074,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -4065,13 +4085,13 @@
         <v>106.673</v>
       </c>
       <c r="D8">
-        <v>10.3624</v>
+        <v>10.362399999999999</v>
       </c>
       <c r="E8" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -4088,7 +4108,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -4096,7 +4116,7 @@
         <v>23</v>
       </c>
       <c r="C10">
-        <v>106.757</v>
+        <v>106.75700000000001</v>
       </c>
       <c r="D10">
         <v>10.3543</v>
@@ -4105,7 +4125,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -4122,7 +4142,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -4133,13 +4153,13 @@
         <v>106.625</v>
       </c>
       <c r="D12">
-        <v>10.4143</v>
+        <v>10.414300000000001</v>
       </c>
       <c r="E12" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -4147,16 +4167,16 @@
         <v>26</v>
       </c>
       <c r="C13">
-        <v>106.716</v>
+        <v>106.71599999999999</v>
       </c>
       <c r="D13">
-        <v>10.4302</v>
+        <v>10.430199999999999</v>
       </c>
       <c r="E13" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -4164,16 +4184,16 @@
         <v>27</v>
       </c>
       <c r="C14">
-        <v>106.757</v>
+        <v>106.75700000000001</v>
       </c>
       <c r="D14">
-        <v>10.3518</v>
+        <v>10.351800000000001</v>
       </c>
       <c r="E14" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -4184,13 +4204,13 @@
         <v>106.754</v>
       </c>
       <c r="D15">
-        <v>10.3289</v>
+        <v>10.328900000000001</v>
       </c>
       <c r="E15" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -4198,16 +4218,16 @@
         <v>29</v>
       </c>
       <c r="C16">
-        <v>106.722</v>
+        <v>106.72199999999999</v>
       </c>
       <c r="D16">
-        <v>10.4585</v>
+        <v>10.458500000000001</v>
       </c>
       <c r="E16" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -4215,7 +4235,7 @@
         <v>30</v>
       </c>
       <c r="C17">
-        <v>105.972</v>
+        <v>105.97199999999999</v>
       </c>
       <c r="D17">
         <v>10.7494</v>
@@ -4224,7 +4244,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -4235,13 +4255,13 @@
         <v>106.324</v>
       </c>
       <c r="D18">
-        <v>10.6535</v>
+        <v>10.653499999999999</v>
       </c>
       <c r="E18" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -4258,7 +4278,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -4266,7 +4286,7 @@
         <v>33</v>
       </c>
       <c r="C20">
-        <v>106.046</v>
+        <v>106.04600000000001</v>
       </c>
       <c r="D20">
         <v>10.6166</v>
@@ -4275,7 +4295,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -4286,13 +4306,13 @@
         <v>105.92</v>
       </c>
       <c r="D21">
-        <v>10.781</v>
+        <v>10.781000000000001</v>
       </c>
       <c r="E21" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -4309,7 +4329,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -4326,7 +4346,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -4343,7 +4363,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -4354,13 +4374,13 @@
         <v>105.883</v>
       </c>
       <c r="D25">
-        <v>10.6391</v>
+        <v>10.639099999999999</v>
       </c>
       <c r="E25" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -4371,13 +4391,13 @@
         <v>106.163</v>
       </c>
       <c r="D26">
-        <v>10.9296</v>
+        <v>10.929600000000001</v>
       </c>
       <c r="E26" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -4394,7 +4414,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -4402,16 +4422,16 @@
         <v>41</v>
       </c>
       <c r="C28">
-        <v>105.653</v>
+        <v>105.65300000000001</v>
       </c>
       <c r="D28">
-        <v>10.8755</v>
+        <v>10.875500000000001</v>
       </c>
       <c r="E28" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -4428,7 +4448,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -4445,7 +4465,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -4462,7 +4482,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -4479,7 +4499,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -4496,7 +4516,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -4504,16 +4524,16 @@
         <v>47</v>
       </c>
       <c r="C34">
-        <v>106.397</v>
+        <v>106.39700000000001</v>
       </c>
       <c r="D34">
-        <v>10.5996</v>
+        <v>10.599600000000001</v>
       </c>
       <c r="E34" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -4521,16 +4541,16 @@
         <v>48</v>
       </c>
       <c r="C35">
-        <v>106.061</v>
+        <v>106.06100000000001</v>
       </c>
       <c r="D35">
-        <v>10.6123</v>
+        <v>10.612299999999999</v>
       </c>
       <c r="E35" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -4541,13 +4561,13 @@
         <v>106</v>
       </c>
       <c r="D36">
-        <v>10.729</v>
+        <v>10.728999999999999</v>
       </c>
       <c r="E36" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -4558,13 +4578,13 @@
         <v>106.315</v>
       </c>
       <c r="D37">
-        <v>10.9067</v>
+        <v>10.906700000000001</v>
       </c>
       <c r="E37" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -4581,7 +4601,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -4592,13 +4612,13 @@
         <v>105.931</v>
       </c>
       <c r="D39">
-        <v>10.7838</v>
+        <v>10.783799999999999</v>
       </c>
       <c r="E39" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -4615,7 +4635,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -4632,7 +4652,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -4649,7 +4669,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -4666,7 +4686,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -4677,13 +4697,13 @@
         <v>106.01</v>
       </c>
       <c r="D44">
-        <v>10.5491</v>
+        <v>10.549099999999999</v>
       </c>
       <c r="E44" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -4691,7 +4711,7 @@
         <v>58</v>
       </c>
       <c r="C45">
-        <v>105.832</v>
+        <v>105.83199999999999</v>
       </c>
       <c r="D45">
         <v>10.6487</v>
@@ -4700,7 +4720,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -4711,15 +4731,15 @@
         <v>106.012</v>
       </c>
       <c r="D46">
-        <v>10.8411</v>
+        <v>10.841100000000001</v>
       </c>
       <c r="E46" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
         <v>60</v>
@@ -4728,13 +4748,13 @@
         <v>105.545</v>
       </c>
       <c r="D47">
-        <v>10.2588</v>
+        <v>10.258800000000001</v>
       </c>
       <c r="E47" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -4751,7 +4771,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -4762,13 +4782,13 @@
         <v>105.81</v>
       </c>
       <c r="D49">
-        <v>10.937</v>
+        <v>10.936999999999999</v>
       </c>
       <c r="E49" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -4779,13 +4799,13 @@
         <v>105.93</v>
       </c>
       <c r="D50">
-        <v>10.7838</v>
+        <v>10.783799999999999</v>
       </c>
       <c r="E50" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -4802,7 +4822,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -4813,30 +4833,30 @@
         <v>106.126</v>
       </c>
       <c r="D52">
-        <v>10.6932</v>
+        <v>10.693199999999999</v>
       </c>
       <c r="E52" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s">
         <v>66</v>
       </c>
       <c r="C53">
-        <v>105.787</v>
+        <v>105.78700000000001</v>
       </c>
       <c r="D53">
-        <v>10.0346</v>
+        <v>10.034599999999999</v>
       </c>
       <c r="E53" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -4853,7 +4873,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -4864,13 +4884,13 @@
         <v>106.229</v>
       </c>
       <c r="D55">
-        <v>10.8976</v>
+        <v>10.897600000000001</v>
       </c>
       <c r="E55" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -4887,7 +4907,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -4904,7 +4924,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -4921,7 +4941,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -4929,16 +4949,16 @@
         <v>72</v>
       </c>
       <c r="C59">
-        <v>105.936</v>
+        <v>105.93600000000001</v>
       </c>
       <c r="D59">
-        <v>10.8234</v>
+        <v>10.823399999999999</v>
       </c>
       <c r="E59" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -4955,7 +4975,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -4972,7 +4992,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -4983,13 +5003,13 @@
         <v>105.932</v>
       </c>
       <c r="D62">
-        <v>10.7769</v>
+        <v>10.776899999999999</v>
       </c>
       <c r="E62" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -4997,7 +5017,7 @@
         <v>76</v>
       </c>
       <c r="C63">
-        <v>105.808</v>
+        <v>105.80800000000001</v>
       </c>
       <c r="D63">
         <v>10.8734</v>
@@ -5006,7 +5026,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -5023,7 +5043,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -5040,7 +5060,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -5051,13 +5071,13 @@
         <v>105.89</v>
       </c>
       <c r="D66">
-        <v>10.838</v>
+        <v>10.837999999999999</v>
       </c>
       <c r="E66" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -5068,13 +5088,13 @@
         <v>106.011</v>
       </c>
       <c r="D67">
-        <v>10.7351</v>
+        <v>10.735099999999999</v>
       </c>
       <c r="E67" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -5091,7 +5111,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -5099,16 +5119,16 @@
         <v>82</v>
       </c>
       <c r="C69">
-        <v>106.528</v>
+        <v>106.52800000000001</v>
       </c>
       <c r="D69">
-        <v>10.5248</v>
+        <v>10.524800000000001</v>
       </c>
       <c r="E69" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -5119,13 +5139,13 @@
         <v>106.124</v>
       </c>
       <c r="D70">
-        <v>10.5948</v>
+        <v>10.594799999999999</v>
       </c>
       <c r="E70" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -5133,7 +5153,7 @@
         <v>84</v>
       </c>
       <c r="C71">
-        <v>106.031</v>
+        <v>106.03100000000001</v>
       </c>
       <c r="D71">
         <v>10.5885</v>
@@ -5142,7 +5162,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -5159,7 +5179,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -5170,13 +5190,13 @@
         <v>106.477</v>
       </c>
       <c r="D73">
-        <v>10.5126</v>
+        <v>10.512600000000001</v>
       </c>
       <c r="E73" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -5193,7 +5213,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -5210,7 +5230,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -5218,16 +5238,16 @@
         <v>89</v>
       </c>
       <c r="C76">
-        <v>106.079</v>
+        <v>106.07899999999999</v>
       </c>
       <c r="D76">
-        <v>10.5354</v>
+        <v>10.535399999999999</v>
       </c>
       <c r="E76" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -5244,7 +5264,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -5255,13 +5275,13 @@
         <v>105.121</v>
       </c>
       <c r="D78">
-        <v>10.0552</v>
+        <v>10.055199999999999</v>
       </c>
       <c r="E78" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -5272,13 +5292,13 @@
         <v>105.276</v>
       </c>
       <c r="D79">
-        <v>9.72758</v>
+        <v>9.7275799999999997</v>
       </c>
       <c r="E79" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -5295,7 +5315,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>8</v>
       </c>
@@ -5303,7 +5323,7 @@
         <v>94</v>
       </c>
       <c r="C81">
-        <v>105.213</v>
+        <v>105.21299999999999</v>
       </c>
       <c r="D81">
         <v>10.1265</v>
@@ -5312,7 +5332,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>8</v>
       </c>
@@ -5320,16 +5340,16 @@
         <v>95</v>
       </c>
       <c r="C82">
-        <v>105.046</v>
+        <v>105.04600000000001</v>
       </c>
       <c r="D82">
-        <v>10.0849</v>
+        <v>10.084899999999999</v>
       </c>
       <c r="E82" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -5337,7 +5357,7 @@
         <v>96</v>
       </c>
       <c r="C83">
-        <v>105.067</v>
+        <v>105.06699999999999</v>
       </c>
       <c r="D83">
         <v>10.0581</v>
@@ -5346,7 +5366,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -5357,13 +5377,13 @@
         <v>105.214</v>
       </c>
       <c r="D84">
-        <v>9.929449999999999</v>
+        <v>9.9294499999999992</v>
       </c>
       <c r="E84" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>8</v>
       </c>
@@ -5380,7 +5400,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -5388,16 +5408,16 @@
         <v>99</v>
       </c>
       <c r="C86">
-        <v>105.243</v>
+        <v>105.24299999999999</v>
       </c>
       <c r="D86">
-        <v>10.0445</v>
+        <v>10.044499999999999</v>
       </c>
       <c r="E86" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>8</v>
       </c>
@@ -5405,16 +5425,16 @@
         <v>100</v>
       </c>
       <c r="C87">
-        <v>105.231</v>
+        <v>105.23099999999999</v>
       </c>
       <c r="D87">
-        <v>10.0316</v>
+        <v>10.031599999999999</v>
       </c>
       <c r="E87" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -5422,7 +5442,7 @@
         <v>101</v>
       </c>
       <c r="C88">
-        <v>105.225</v>
+        <v>105.22499999999999</v>
       </c>
       <c r="D88">
         <v>10.1173</v>
@@ -5431,7 +5451,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>8</v>
       </c>
@@ -5442,13 +5462,13 @@
         <v>105.009</v>
       </c>
       <c r="D89">
-        <v>10.1322</v>
+        <v>10.132199999999999</v>
       </c>
       <c r="E89" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>8</v>
       </c>
@@ -5459,13 +5479,13 @@
         <v>105.121</v>
       </c>
       <c r="D90">
-        <v>10.0551</v>
+        <v>10.055099999999999</v>
       </c>
       <c r="E90" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>8</v>
       </c>
@@ -5476,13 +5496,13 @@
         <v>105.099</v>
       </c>
       <c r="D91">
-        <v>10.1443</v>
+        <v>10.144299999999999</v>
       </c>
       <c r="E91" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>8</v>
       </c>
@@ -5499,7 +5519,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -5507,7 +5527,7 @@
         <v>106</v>
       </c>
       <c r="C93">
-        <v>105.266</v>
+        <v>105.26600000000001</v>
       </c>
       <c r="D93">
         <v>10.1815</v>
@@ -5516,7 +5536,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -5533,7 +5553,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -5541,16 +5561,16 @@
         <v>108</v>
       </c>
       <c r="C95">
-        <v>105.231</v>
+        <v>105.23099999999999</v>
       </c>
       <c r="D95">
-        <v>10.0681</v>
+        <v>10.068099999999999</v>
       </c>
       <c r="E95" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -5558,7 +5578,7 @@
         <v>109</v>
       </c>
       <c r="C96">
-        <v>105.237</v>
+        <v>105.23699999999999</v>
       </c>
       <c r="D96">
         <v>10.0679</v>
@@ -5567,7 +5587,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>8</v>
       </c>
@@ -5575,16 +5595,16 @@
         <v>110</v>
       </c>
       <c r="C97">
-        <v>105.162</v>
+        <v>105.16200000000001</v>
       </c>
       <c r="D97">
-        <v>9.90569</v>
+        <v>9.9056899999999999</v>
       </c>
       <c r="E97" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>8</v>
       </c>
@@ -5601,7 +5621,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -5612,13 +5632,13 @@
         <v>105.31</v>
       </c>
       <c r="D99">
-        <v>10.0049</v>
+        <v>10.004899999999999</v>
       </c>
       <c r="E99" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -5629,13 +5649,13 @@
         <v>105.268</v>
       </c>
       <c r="D100">
-        <v>9.790319999999999</v>
+        <v>9.7903199999999995</v>
       </c>
       <c r="E100" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>8</v>
       </c>
@@ -5646,13 +5666,13 @@
         <v>105.095</v>
       </c>
       <c r="D101">
-        <v>9.77234</v>
+        <v>9.7723399999999998</v>
       </c>
       <c r="E101" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -5660,16 +5680,16 @@
         <v>115</v>
       </c>
       <c r="C102">
-        <v>105.269</v>
+        <v>105.26900000000001</v>
       </c>
       <c r="D102">
-        <v>9.79022</v>
+        <v>9.7902199999999997</v>
       </c>
       <c r="E102" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -5680,13 +5700,13 @@
         <v>105.34</v>
       </c>
       <c r="D103">
-        <v>10.0559</v>
+        <v>10.055899999999999</v>
       </c>
       <c r="E103" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -5703,7 +5723,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -5711,16 +5731,16 @@
         <v>118</v>
       </c>
       <c r="C105">
-        <v>105.272</v>
+        <v>105.27200000000001</v>
       </c>
       <c r="D105">
-        <v>9.986840000000001</v>
+        <v>9.9868400000000008</v>
       </c>
       <c r="E105" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -5731,13 +5751,13 @@
         <v>105.233</v>
       </c>
       <c r="D106">
-        <v>9.821949999999999</v>
+        <v>9.8219499999999993</v>
       </c>
       <c r="E106" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -5748,13 +5768,13 @@
         <v>105.31</v>
       </c>
       <c r="D107">
-        <v>9.952500000000001</v>
+        <v>9.9525000000000006</v>
       </c>
       <c r="E107" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -5765,13 +5785,13 @@
         <v>105.267</v>
       </c>
       <c r="D108">
-        <v>9.82433</v>
+        <v>9.8243299999999998</v>
       </c>
       <c r="E108" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -5779,16 +5799,16 @@
         <v>122</v>
       </c>
       <c r="C109">
-        <v>105.135</v>
+        <v>105.13500000000001</v>
       </c>
       <c r="D109">
-        <v>10.0781</v>
+        <v>10.078099999999999</v>
       </c>
       <c r="E109" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -5796,7 +5816,7 @@
         <v>123</v>
       </c>
       <c r="C110">
-        <v>104.799</v>
+        <v>104.79900000000001</v>
       </c>
       <c r="D110">
         <v>10.2712</v>
@@ -5805,7 +5825,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -5822,7 +5842,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -5839,7 +5859,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -5850,13 +5870,13 @@
         <v>105.108</v>
       </c>
       <c r="D113">
-        <v>10.1545</v>
+        <v>10.154500000000001</v>
       </c>
       <c r="E113" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -5867,13 +5887,13 @@
         <v>104.86</v>
       </c>
       <c r="D114">
-        <v>10.2313</v>
+        <v>10.231299999999999</v>
       </c>
       <c r="E114" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -5881,7 +5901,7 @@
         <v>128</v>
       </c>
       <c r="C115">
-        <v>104.957</v>
+        <v>104.95699999999999</v>
       </c>
       <c r="D115">
         <v>10.1698</v>
@@ -5890,7 +5910,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -5907,7 +5927,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -5918,13 +5938,13 @@
         <v>105.304</v>
       </c>
       <c r="D117">
-        <v>9.93383</v>
+        <v>9.9338300000000004</v>
       </c>
       <c r="E117" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -5935,13 +5955,13 @@
         <v>105.047</v>
       </c>
       <c r="D118">
-        <v>10.1583</v>
+        <v>10.158300000000001</v>
       </c>
       <c r="E118" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>8</v>
       </c>
@@ -5949,16 +5969,16 @@
         <v>132</v>
       </c>
       <c r="C119">
-        <v>105.237</v>
+        <v>105.23699999999999</v>
       </c>
       <c r="D119">
-        <v>9.917540000000001</v>
+        <v>9.9175400000000007</v>
       </c>
       <c r="E119" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -5969,13 +5989,13 @@
         <v>105.38</v>
       </c>
       <c r="D120">
-        <v>9.8154</v>
+        <v>9.8154000000000003</v>
       </c>
       <c r="E120" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -5986,13 +6006,13 @@
         <v>105.31</v>
       </c>
       <c r="D121">
-        <v>9.905720000000001</v>
+        <v>9.9057200000000005</v>
       </c>
       <c r="E121" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -6003,13 +6023,13 @@
         <v>105.197</v>
       </c>
       <c r="D122">
-        <v>10.0277</v>
+        <v>10.027699999999999</v>
       </c>
       <c r="E122" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>8</v>
       </c>
@@ -6020,13 +6040,13 @@
         <v>105.315</v>
       </c>
       <c r="D123">
-        <v>9.910869999999999</v>
+        <v>9.9108699999999992</v>
       </c>
       <c r="E123" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>8</v>
       </c>
@@ -6043,7 +6063,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>8</v>
       </c>
@@ -6054,13 +6074,13 @@
         <v>105.285</v>
       </c>
       <c r="D125">
-        <v>10.0971</v>
+        <v>10.097099999999999</v>
       </c>
       <c r="E125" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>8</v>
       </c>
@@ -6077,7 +6097,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>8</v>
       </c>
@@ -6088,13 +6108,13 @@
         <v>105.444</v>
       </c>
       <c r="D127">
-        <v>9.99934</v>
+        <v>9.9993400000000001</v>
       </c>
       <c r="E127" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -6105,13 +6125,13 @@
         <v>105.176</v>
       </c>
       <c r="D128">
-        <v>9.94448</v>
+        <v>9.9444800000000004</v>
       </c>
       <c r="E128" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>8</v>
       </c>
@@ -6122,13 +6142,13 @@
         <v>105.238</v>
       </c>
       <c r="D129">
-        <v>9.917759999999999</v>
+        <v>9.9177599999999995</v>
       </c>
       <c r="E129" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>8</v>
       </c>
@@ -6136,16 +6156,16 @@
         <v>143</v>
       </c>
       <c r="C130">
-        <v>105.344</v>
+        <v>105.34399999999999</v>
       </c>
       <c r="D130">
-        <v>9.962540000000001</v>
+        <v>9.9625400000000006</v>
       </c>
       <c r="E130" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>8</v>
       </c>
@@ -6162,7 +6182,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>8</v>
       </c>
@@ -6173,13 +6193,13 @@
         <v>105.307</v>
       </c>
       <c r="D132">
-        <v>9.931979999999999</v>
+        <v>9.9319799999999994</v>
       </c>
       <c r="E132" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>8</v>
       </c>
@@ -6196,7 +6216,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>8</v>
       </c>
@@ -6213,7 +6233,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -6224,13 +6244,13 @@
         <v>104.86</v>
       </c>
       <c r="D135">
-        <v>10.229</v>
+        <v>10.228999999999999</v>
       </c>
       <c r="E135" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>8</v>
       </c>
@@ -6241,13 +6261,13 @@
         <v>105.08</v>
       </c>
       <c r="D136">
-        <v>10.1103</v>
+        <v>10.110300000000001</v>
       </c>
       <c r="E136" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -6264,7 +6284,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>8</v>
       </c>
@@ -6275,13 +6295,13 @@
         <v>105.224</v>
       </c>
       <c r="D138">
-        <v>9.74766</v>
+        <v>9.7476599999999998</v>
       </c>
       <c r="E138" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -6292,13 +6312,13 @@
         <v>105.316</v>
       </c>
       <c r="D139">
-        <v>9.773669999999999</v>
+        <v>9.7736699999999992</v>
       </c>
       <c r="E139" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>8</v>
       </c>
@@ -6315,7 +6335,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -6332,7 +6352,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -6340,7 +6360,7 @@
         <v>155</v>
       </c>
       <c r="C142">
-        <v>104.784</v>
+        <v>104.78400000000001</v>
       </c>
       <c r="D142">
         <v>10.2813</v>
@@ -6349,7 +6369,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -6360,13 +6380,13 @@
         <v>105.447</v>
       </c>
       <c r="D143">
-        <v>10.0033</v>
+        <v>10.003299999999999</v>
       </c>
       <c r="E143" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -6383,7 +6403,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>8</v>
       </c>
@@ -6391,16 +6411,16 @@
         <v>158</v>
       </c>
       <c r="C145">
-        <v>104.829</v>
+        <v>104.82899999999999</v>
       </c>
       <c r="D145">
-        <v>10.3008</v>
+        <v>10.300800000000001</v>
       </c>
       <c r="E145" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>8</v>
       </c>
@@ -6408,16 +6428,16 @@
         <v>159</v>
       </c>
       <c r="C146">
-        <v>104.981</v>
+        <v>104.98099999999999</v>
       </c>
       <c r="D146">
-        <v>10.2648</v>
+        <v>10.264799999999999</v>
       </c>
       <c r="E146" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -6434,7 +6454,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -6445,13 +6465,13 @@
         <v>105.39</v>
       </c>
       <c r="D148">
-        <v>9.96846</v>
+        <v>9.9684600000000003</v>
       </c>
       <c r="E148" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>8</v>
       </c>
@@ -6462,13 +6482,13 @@
         <v>105.188</v>
       </c>
       <c r="D149">
-        <v>9.81771</v>
+        <v>9.8177099999999999</v>
       </c>
       <c r="E149" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>8</v>
       </c>
@@ -6479,13 +6499,13 @@
         <v>105.373</v>
       </c>
       <c r="D150">
-        <v>9.744059999999999</v>
+        <v>9.7440599999999993</v>
       </c>
       <c r="E150" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>8</v>
       </c>
@@ -6496,13 +6516,13 @@
         <v>104.807</v>
       </c>
       <c r="D151">
-        <v>10.2687</v>
+        <v>10.268700000000001</v>
       </c>
       <c r="E151" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>8</v>
       </c>
@@ -6510,7 +6530,7 @@
         <v>165</v>
       </c>
       <c r="C152">
-        <v>105.406</v>
+        <v>105.40600000000001</v>
       </c>
       <c r="D152">
         <v>10.0106</v>
@@ -6519,7 +6539,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>8</v>
       </c>
@@ -6527,16 +6547,16 @@
         <v>166</v>
       </c>
       <c r="C153">
-        <v>104.716</v>
+        <v>104.71599999999999</v>
       </c>
       <c r="D153">
-        <v>10.4266</v>
+        <v>10.426600000000001</v>
       </c>
       <c r="E153" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>8</v>
       </c>
@@ -6547,13 +6567,13 @@
         <v>104.968</v>
       </c>
       <c r="D154">
-        <v>10.2452</v>
+        <v>10.245200000000001</v>
       </c>
       <c r="E154" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>8</v>
       </c>
@@ -6561,7 +6581,7 @@
         <v>168</v>
       </c>
       <c r="C155">
-        <v>105.088</v>
+        <v>105.08799999999999</v>
       </c>
       <c r="D155">
         <v>10.0631</v>
@@ -6570,7 +6590,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>8</v>
       </c>
@@ -6578,7 +6598,7 @@
         <v>169</v>
       </c>
       <c r="C156">
-        <v>105.332</v>
+        <v>105.33199999999999</v>
       </c>
       <c r="D156">
         <v>10.0444</v>
@@ -6587,7 +6607,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -6598,13 +6618,13 @@
         <v>104.67</v>
       </c>
       <c r="D157">
-        <v>10.351</v>
+        <v>10.351000000000001</v>
       </c>
       <c r="E157" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>8</v>
       </c>
@@ -6615,13 +6635,13 @@
         <v>105.185</v>
       </c>
       <c r="D158">
-        <v>9.60515</v>
+        <v>9.6051500000000001</v>
       </c>
       <c r="E158" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>8</v>
       </c>
@@ -6629,7 +6649,7 @@
         <v>172</v>
       </c>
       <c r="C159">
-        <v>105.243</v>
+        <v>105.24299999999999</v>
       </c>
       <c r="D159">
         <v>10.0442</v>
@@ -6638,7 +6658,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>8</v>
       </c>
@@ -6655,7 +6675,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>8</v>
       </c>
@@ -6672,7 +6692,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>8</v>
       </c>
@@ -6680,7 +6700,7 @@
         <v>175</v>
       </c>
       <c r="C162">
-        <v>105.046</v>
+        <v>105.04600000000001</v>
       </c>
       <c r="D162">
         <v>10.0848</v>
@@ -6689,7 +6709,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>8</v>
       </c>
@@ -6697,18 +6717,18 @@
         <v>176</v>
       </c>
       <c r="C163">
-        <v>105.091</v>
+        <v>105.09099999999999</v>
       </c>
       <c r="D163">
-        <v>9.994210000000001</v>
+        <v>9.9942100000000007</v>
       </c>
       <c r="E163" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B164" t="s">
         <v>177</v>
@@ -6717,13 +6737,13 @@
         <v>106.6751898</v>
       </c>
       <c r="D164">
-        <v>10.7893532</v>
+        <v>10.789353200000001</v>
       </c>
       <c r="E164" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>8</v>
       </c>
@@ -6731,16 +6751,16 @@
         <v>90</v>
       </c>
       <c r="C165">
-        <v>105.321042</v>
+        <v>105.32104200000001</v>
       </c>
       <c r="D165">
-        <v>9.773463</v>
+        <v>9.7734629999999996</v>
       </c>
       <c r="E165" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>10</v>
       </c>
@@ -6748,16 +6768,16 @@
         <v>178</v>
       </c>
       <c r="C166">
-        <v>106.353</v>
+        <v>106.35299999999999</v>
       </c>
       <c r="D166">
-        <v>9.84582</v>
+        <v>9.8458199999999998</v>
       </c>
       <c r="E166" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>10</v>
       </c>
@@ -6768,13 +6788,13 @@
         <v>106.196</v>
       </c>
       <c r="D167">
-        <v>9.81765</v>
+        <v>9.8176500000000004</v>
       </c>
       <c r="E167" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -6782,16 +6802,16 @@
         <v>180</v>
       </c>
       <c r="C168">
-        <v>106.257</v>
+        <v>106.25700000000001</v>
       </c>
       <c r="D168">
-        <v>9.73781</v>
+        <v>9.7378099999999996</v>
       </c>
       <c r="E168" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>10</v>
       </c>
@@ -6802,13 +6822,13 @@
         <v>106.087</v>
       </c>
       <c r="D169">
-        <v>9.83911</v>
+        <v>9.8391099999999998</v>
       </c>
       <c r="E169" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -6819,13 +6839,13 @@
         <v>106.152</v>
       </c>
       <c r="D170">
-        <v>9.91093</v>
+        <v>9.9109300000000005</v>
       </c>
       <c r="E170" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -6836,13 +6856,13 @@
         <v>106.15</v>
       </c>
       <c r="D171">
-        <v>9.865069999999999</v>
+        <v>9.8650699999999993</v>
       </c>
       <c r="E171" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>10</v>
       </c>
@@ -6850,16 +6870,16 @@
         <v>184</v>
       </c>
       <c r="C172">
-        <v>106.165</v>
+        <v>106.16500000000001</v>
       </c>
       <c r="D172">
-        <v>9.84046</v>
+        <v>9.8404600000000002</v>
       </c>
       <c r="E172" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>10</v>
       </c>
@@ -6867,16 +6887,16 @@
         <v>185</v>
       </c>
       <c r="C173">
-        <v>106.243</v>
+        <v>106.24299999999999</v>
       </c>
       <c r="D173">
-        <v>9.95964</v>
+        <v>9.9596400000000003</v>
       </c>
       <c r="E173" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -6893,7 +6913,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>10</v>
       </c>
@@ -6904,13 +6924,13 @@
         <v>106.36</v>
       </c>
       <c r="D175">
-        <v>9.7316</v>
+        <v>9.7316000000000003</v>
       </c>
       <c r="E175" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>10</v>
       </c>
@@ -6918,16 +6938,16 @@
         <v>188</v>
       </c>
       <c r="C176">
-        <v>106.275</v>
+        <v>106.27500000000001</v>
       </c>
       <c r="D176">
-        <v>9.869910000000001</v>
+        <v>9.8699100000000008</v>
       </c>
       <c r="E176" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>10</v>
       </c>
@@ -6935,16 +6955,16 @@
         <v>189</v>
       </c>
       <c r="C177">
-        <v>106.257</v>
+        <v>106.25700000000001</v>
       </c>
       <c r="D177">
-        <v>9.812480000000001</v>
+        <v>9.8124800000000008</v>
       </c>
       <c r="E177" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>10</v>
       </c>
@@ -6955,13 +6975,13 @@
         <v>106.416</v>
       </c>
       <c r="D178">
-        <v>9.75332</v>
+        <v>9.7533200000000004</v>
       </c>
       <c r="E178" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>10</v>
       </c>
@@ -6972,13 +6992,13 @@
         <v>106.211</v>
       </c>
       <c r="D179">
-        <v>9.97565</v>
+        <v>9.9756499999999999</v>
       </c>
       <c r="E179" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>10</v>
       </c>
@@ -6986,7 +7006,7 @@
         <v>192</v>
       </c>
       <c r="C180">
-        <v>106.061</v>
+        <v>106.06100000000001</v>
       </c>
       <c r="D180">
         <v>10.1229</v>
@@ -6995,7 +7015,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>10</v>
       </c>
@@ -7006,13 +7026,13 @@
         <v>106.083</v>
       </c>
       <c r="D181">
-        <v>10.0109</v>
+        <v>10.010899999999999</v>
       </c>
       <c r="E181" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>10</v>
       </c>
@@ -7023,13 +7043,13 @@
         <v>106.1</v>
       </c>
       <c r="D182">
-        <v>10.0005</v>
+        <v>10.000500000000001</v>
       </c>
       <c r="E182" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>10</v>
       </c>
@@ -7040,13 +7060,13 @@
         <v>106.19</v>
       </c>
       <c r="D183">
-        <v>9.8177</v>
+        <v>9.8177000000000003</v>
       </c>
       <c r="E183" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -7057,13 +7077,13 @@
         <v>106.084</v>
       </c>
       <c r="D184">
-        <v>10.1301</v>
+        <v>10.130100000000001</v>
       </c>
       <c r="E184" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>10</v>
       </c>
@@ -7074,13 +7094,13 @@
         <v>106.041</v>
       </c>
       <c r="D185">
-        <v>9.99812</v>
+        <v>9.9981200000000001</v>
       </c>
       <c r="E185" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>10</v>
       </c>
@@ -7088,7 +7108,7 @@
         <v>198</v>
       </c>
       <c r="C186">
-        <v>106.177</v>
+        <v>106.17700000000001</v>
       </c>
       <c r="D186">
         <v>9.94421</v>
@@ -7097,7 +7117,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>10</v>
       </c>
@@ -7108,13 +7128,13 @@
         <v>106.261</v>
       </c>
       <c r="D187">
-        <v>9.739520000000001</v>
+        <v>9.7395200000000006</v>
       </c>
       <c r="E187" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>10</v>
       </c>
@@ -7125,13 +7145,13 @@
         <v>106.36</v>
       </c>
       <c r="D188">
-        <v>9.7689</v>
+        <v>9.7689000000000004</v>
       </c>
       <c r="E188" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>10</v>
       </c>
@@ -7142,13 +7162,13 @@
         <v>106.244</v>
       </c>
       <c r="D189">
-        <v>9.96067</v>
+        <v>9.9606700000000004</v>
       </c>
       <c r="E189" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>10</v>
       </c>
@@ -7159,13 +7179,13 @@
         <v>106.24</v>
       </c>
       <c r="D190">
-        <v>9.870200000000001</v>
+        <v>9.8702000000000005</v>
       </c>
       <c r="E190" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>10</v>
       </c>
@@ -7176,13 +7196,13 @@
         <v>106.276</v>
       </c>
       <c r="D191">
-        <v>9.87893</v>
+        <v>9.8789300000000004</v>
       </c>
       <c r="E191" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>10</v>
       </c>
@@ -7193,13 +7213,13 @@
         <v>106.126</v>
       </c>
       <c r="D192">
-        <v>9.83897</v>
+        <v>9.8389699999999998</v>
       </c>
       <c r="E192" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>10</v>
       </c>
@@ -7210,13 +7230,13 @@
         <v>106.083</v>
       </c>
       <c r="D193">
-        <v>9.95979</v>
+        <v>9.9597899999999999</v>
       </c>
       <c r="E193" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -7227,13 +7247,13 @@
         <v>106.276</v>
       </c>
       <c r="D194">
-        <v>9.807320000000001</v>
+        <v>9.8073200000000007</v>
       </c>
       <c r="E194" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>10</v>
       </c>
@@ -7244,13 +7264,13 @@
         <v>106.361</v>
       </c>
       <c r="D195">
-        <v>9.94084</v>
+        <v>9.9408399999999997</v>
       </c>
       <c r="E195" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>10</v>
       </c>
@@ -7261,13 +7281,13 @@
         <v>106.343</v>
       </c>
       <c r="D196">
-        <v>9.702109999999999</v>
+        <v>9.7021099999999993</v>
       </c>
       <c r="E196" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -7275,16 +7295,16 @@
         <v>209</v>
       </c>
       <c r="C197">
-        <v>106.165</v>
+        <v>106.16500000000001</v>
       </c>
       <c r="D197">
-        <v>9.840210000000001</v>
+        <v>9.8402100000000008</v>
       </c>
       <c r="E197" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -7295,13 +7315,13 @@
         <v>106.39</v>
       </c>
       <c r="D198">
-        <v>9.711499999999999</v>
+        <v>9.7114999999999991</v>
       </c>
       <c r="E198" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -7312,13 +7332,13 @@
         <v>106.292</v>
       </c>
       <c r="D199">
-        <v>9.670909999999999</v>
+        <v>9.6709099999999992</v>
       </c>
       <c r="E199" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>10</v>
       </c>
@@ -7326,7 +7346,7 @@
         <v>212</v>
       </c>
       <c r="C200">
-        <v>105.993</v>
+        <v>105.99299999999999</v>
       </c>
       <c r="D200">
         <v>10.2881</v>
@@ -7335,7 +7355,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -7352,7 +7372,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>10</v>
       </c>
@@ -7363,13 +7383,13 @@
         <v>105.883</v>
       </c>
       <c r="D202">
-        <v>9.994450000000001</v>
+        <v>9.9944500000000005</v>
       </c>
       <c r="E202" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>10</v>
       </c>
@@ -7377,7 +7397,7 @@
         <v>215</v>
       </c>
       <c r="C203">
-        <v>105.933</v>
+        <v>105.93300000000001</v>
       </c>
       <c r="D203">
         <v>10.2355</v>
@@ -7386,7 +7406,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>10</v>
       </c>
@@ -7403,7 +7423,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>10</v>
       </c>
@@ -7420,7 +7440,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -7437,7 +7457,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>10</v>
       </c>
@@ -7445,7 +7465,7 @@
         <v>219</v>
       </c>
       <c r="C207">
-        <v>105.772</v>
+        <v>105.77200000000001</v>
       </c>
       <c r="D207">
         <v>10.1738</v>
@@ -7454,7 +7474,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>10</v>
       </c>
@@ -7471,7 +7491,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -7488,7 +7508,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -7505,7 +7525,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -7513,16 +7533,16 @@
         <v>223</v>
       </c>
       <c r="C211">
-        <v>105.832</v>
+        <v>105.83199999999999</v>
       </c>
       <c r="D211">
-        <v>10.0828</v>
+        <v>10.082800000000001</v>
       </c>
       <c r="E211" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>10</v>
       </c>
@@ -7533,13 +7553,13 @@
         <v>105.904</v>
       </c>
       <c r="D212">
-        <v>10.0455</v>
+        <v>10.045500000000001</v>
       </c>
       <c r="E212" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -7550,13 +7570,13 @@
         <v>105.976</v>
       </c>
       <c r="D213">
-        <v>10.2078</v>
+        <v>10.207800000000001</v>
       </c>
       <c r="E213" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -7567,13 +7587,13 @@
         <v>106.383</v>
       </c>
       <c r="D214">
-        <v>9.657170000000001</v>
+        <v>9.6571700000000007</v>
       </c>
       <c r="E214" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -7590,7 +7610,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -7601,13 +7621,13 @@
         <v>106.22</v>
       </c>
       <c r="D216">
-        <v>9.781599999999999</v>
+        <v>9.7815999999999992</v>
       </c>
       <c r="E216" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>10</v>
       </c>
@@ -7618,13 +7638,13 @@
         <v>106.389</v>
       </c>
       <c r="D217">
-        <v>9.755319999999999</v>
+        <v>9.7553199999999993</v>
       </c>
       <c r="E217" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>10</v>
       </c>
@@ -7635,13 +7655,13 @@
         <v>106.11</v>
       </c>
       <c r="D218">
-        <v>10.0302</v>
+        <v>10.030200000000001</v>
       </c>
       <c r="E218" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>10</v>
       </c>
@@ -7652,13 +7672,13 @@
         <v>105.973</v>
       </c>
       <c r="D219">
-        <v>10.0483</v>
+        <v>10.048299999999999</v>
       </c>
       <c r="E219" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>10</v>
       </c>
@@ -7675,7 +7695,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>10</v>
       </c>
@@ -7692,7 +7712,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>10</v>
       </c>
@@ -7700,16 +7720,16 @@
         <v>234</v>
       </c>
       <c r="C222">
-        <v>106.201</v>
+        <v>106.20099999999999</v>
       </c>
       <c r="D222">
-        <v>9.92623</v>
+        <v>9.9262300000000003</v>
       </c>
       <c r="E222" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>10</v>
       </c>
@@ -7726,7 +7746,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>10</v>
       </c>
@@ -7737,13 +7757,13 @@
         <v>106.152</v>
       </c>
       <c r="D224">
-        <v>10.1108</v>
+        <v>10.110799999999999</v>
       </c>
       <c r="E224" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>10</v>
       </c>
@@ -7754,13 +7774,13 @@
         <v>106.241</v>
       </c>
       <c r="D225">
-        <v>9.917579999999999</v>
+        <v>9.9175799999999992</v>
       </c>
       <c r="E225" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>10</v>
       </c>
@@ -7768,16 +7788,16 @@
         <v>238</v>
       </c>
       <c r="C226">
-        <v>105.862</v>
+        <v>105.86199999999999</v>
       </c>
       <c r="D226">
-        <v>10.1308</v>
+        <v>10.130800000000001</v>
       </c>
       <c r="E226" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>10</v>
       </c>
@@ -7788,13 +7808,13 @@
         <v>106.145</v>
       </c>
       <c r="D227">
-        <v>9.82658</v>
+        <v>9.8265799999999999</v>
       </c>
       <c r="E227" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>10</v>
       </c>
@@ -7805,13 +7825,13 @@
         <v>105.827</v>
       </c>
       <c r="D228">
-        <v>10.1315</v>
+        <v>10.131500000000001</v>
       </c>
       <c r="E228" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>10</v>
       </c>
@@ -7819,7 +7839,7 @@
         <v>241</v>
       </c>
       <c r="C229">
-        <v>106.132</v>
+        <v>106.13200000000001</v>
       </c>
       <c r="D229">
         <v>10.1424</v>
@@ -7828,7 +7848,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>10</v>
       </c>
@@ -7839,13 +7859,13 @@
         <v>105.89</v>
       </c>
       <c r="D230">
-        <v>10.2238</v>
+        <v>10.223800000000001</v>
       </c>
       <c r="E230" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>10</v>
       </c>
@@ -7856,13 +7876,13 @@
         <v>106.241</v>
       </c>
       <c r="D231">
-        <v>9.959860000000001</v>
+        <v>9.9598600000000008</v>
       </c>
       <c r="E231" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>10</v>
       </c>
@@ -7879,7 +7899,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>10</v>
       </c>
@@ -7896,7 +7916,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>10</v>
       </c>
@@ -7907,13 +7927,13 @@
         <v>106.151</v>
       </c>
       <c r="D234">
-        <v>10.0751</v>
+        <v>10.075100000000001</v>
       </c>
       <c r="E234" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>10</v>
       </c>
@@ -7924,13 +7944,13 @@
         <v>105.93</v>
       </c>
       <c r="D235">
-        <v>10.146</v>
+        <v>10.146000000000001</v>
       </c>
       <c r="E235" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -7938,16 +7958,16 @@
         <v>247</v>
       </c>
       <c r="C236">
-        <v>105.885</v>
+        <v>105.88500000000001</v>
       </c>
       <c r="D236">
-        <v>10.0818</v>
+        <v>10.081799999999999</v>
       </c>
       <c r="E236" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>10</v>
       </c>
@@ -7958,13 +7978,13 @@
         <v>105.919</v>
       </c>
       <c r="D237">
-        <v>9.966379999999999</v>
+        <v>9.9663799999999991</v>
       </c>
       <c r="E237" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>10</v>
       </c>
@@ -7975,13 +7995,13 @@
         <v>105.955</v>
       </c>
       <c r="D238">
-        <v>10.1261</v>
+        <v>10.126099999999999</v>
       </c>
       <c r="E238" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>10</v>
       </c>
@@ -7992,13 +8012,13 @@
         <v>106.086</v>
       </c>
       <c r="D239">
-        <v>9.96133</v>
+        <v>9.9613300000000002</v>
       </c>
       <c r="E239" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>10</v>
       </c>
@@ -8009,13 +8029,13 @@
         <v>105.905</v>
       </c>
       <c r="D240">
-        <v>10.0376</v>
+        <v>10.037599999999999</v>
       </c>
       <c r="E240" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>10</v>
       </c>
@@ -8023,7 +8043,7 @@
         <v>252</v>
       </c>
       <c r="C241">
-        <v>105.915</v>
+        <v>105.91500000000001</v>
       </c>
       <c r="D241">
         <v>10.1729</v>
@@ -8032,7 +8052,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>11</v>
       </c>
@@ -8043,13 +8063,13 @@
         <v>105.49</v>
       </c>
       <c r="D242">
-        <v>9.608090000000001</v>
+        <v>9.6080900000000007</v>
       </c>
       <c r="E242" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>11</v>
       </c>
@@ -8060,13 +8080,13 @@
         <v>105.65</v>
       </c>
       <c r="D243">
-        <v>9.8307</v>
+        <v>9.8307000000000002</v>
       </c>
       <c r="E243" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>11</v>
       </c>
@@ -8083,7 +8103,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>11</v>
       </c>
@@ -8091,16 +8111,16 @@
         <v>256</v>
       </c>
       <c r="C245">
-        <v>105.695</v>
+        <v>105.69499999999999</v>
       </c>
       <c r="D245">
-        <v>9.676220000000001</v>
+        <v>9.6762200000000007</v>
       </c>
       <c r="E245" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>11</v>
       </c>
@@ -8111,13 +8131,13 @@
         <v>105.53</v>
       </c>
       <c r="D246">
-        <v>9.680300000000001</v>
+        <v>9.6803000000000008</v>
       </c>
       <c r="E246" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>11</v>
       </c>
@@ -8128,13 +8148,13 @@
         <v>105.678</v>
       </c>
       <c r="D247">
-        <v>9.651339999999999</v>
+        <v>9.6513399999999994</v>
       </c>
       <c r="E247" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>11</v>
       </c>
@@ -8145,13 +8165,13 @@
         <v>105.569</v>
       </c>
       <c r="D248">
-        <v>9.68624</v>
+        <v>9.6862399999999997</v>
       </c>
       <c r="E248" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>11</v>
       </c>
@@ -8162,13 +8182,13 @@
         <v>105.428</v>
       </c>
       <c r="D249">
-        <v>9.682980000000001</v>
+        <v>9.6829800000000006</v>
       </c>
       <c r="E249" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>11</v>
       </c>
@@ -8179,13 +8199,13 @@
         <v>105.598</v>
       </c>
       <c r="D250">
-        <v>9.96527</v>
+        <v>9.9652700000000003</v>
       </c>
       <c r="E250" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>11</v>
       </c>
@@ -8193,16 +8213,16 @@
         <v>262</v>
       </c>
       <c r="C251">
-        <v>105.585</v>
+        <v>105.58499999999999</v>
       </c>
       <c r="D251">
-        <v>9.886659999999999</v>
+        <v>9.8866599999999991</v>
       </c>
       <c r="E251" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>11</v>
       </c>
@@ -8213,13 +8233,13 @@
         <v>105.545</v>
       </c>
       <c r="D252">
-        <v>9.766260000000001</v>
+        <v>9.7662600000000008</v>
       </c>
       <c r="E252" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>11</v>
       </c>
@@ -8227,16 +8247,16 @@
         <v>264</v>
       </c>
       <c r="C253">
-        <v>105.606</v>
+        <v>105.60599999999999</v>
       </c>
       <c r="D253">
-        <v>9.92352</v>
+        <v>9.9235199999999999</v>
       </c>
       <c r="E253" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>11</v>
       </c>
@@ -8244,16 +8264,16 @@
         <v>265</v>
       </c>
       <c r="C254">
-        <v>105.573</v>
+        <v>105.57299999999999</v>
       </c>
       <c r="D254">
-        <v>9.708930000000001</v>
+        <v>9.7089300000000005</v>
       </c>
       <c r="E254" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>11</v>
       </c>
@@ -8264,13 +8284,13 @@
         <v>105.559</v>
       </c>
       <c r="D255">
-        <v>9.675459999999999</v>
+        <v>9.6754599999999993</v>
       </c>
       <c r="E255" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>11</v>
       </c>
@@ -8281,13 +8301,13 @@
         <v>105.59</v>
       </c>
       <c r="D256">
-        <v>9.678699999999999</v>
+        <v>9.6786999999999992</v>
       </c>
       <c r="E256" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>11</v>
       </c>
@@ -8298,13 +8318,13 @@
         <v>105.482</v>
       </c>
       <c r="D257">
-        <v>9.63697</v>
+        <v>9.6369699999999998</v>
       </c>
       <c r="E257" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>11</v>
       </c>
@@ -8312,16 +8332,16 @@
         <v>269</v>
       </c>
       <c r="C258">
-        <v>105.433</v>
+        <v>105.43300000000001</v>
       </c>
       <c r="D258">
-        <v>9.66963</v>
+        <v>9.6696299999999997</v>
       </c>
       <c r="E258" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>11</v>
       </c>
@@ -8332,13 +8352,13 @@
         <v>105.712</v>
       </c>
       <c r="D259">
-        <v>9.814450000000001</v>
+        <v>9.8144500000000008</v>
       </c>
       <c r="E259" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>11</v>
       </c>
@@ -8349,13 +8369,13 @@
         <v>105.708</v>
       </c>
       <c r="D260">
-        <v>9.821160000000001</v>
+        <v>9.8211600000000008</v>
       </c>
       <c r="E260" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>11</v>
       </c>
@@ -8363,16 +8383,16 @@
         <v>272</v>
       </c>
       <c r="C261">
-        <v>105.567</v>
+        <v>105.56699999999999</v>
       </c>
       <c r="D261">
-        <v>9.754020000000001</v>
+        <v>9.7540200000000006</v>
       </c>
       <c r="E261" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -8383,13 +8403,13 @@
         <v>105.539</v>
       </c>
       <c r="D262">
-        <v>9.65258</v>
+        <v>9.6525800000000004</v>
       </c>
       <c r="E262" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>11</v>
       </c>
@@ -8400,13 +8420,13 @@
         <v>105.41</v>
       </c>
       <c r="D263">
-        <v>9.6028</v>
+        <v>9.6028000000000002</v>
       </c>
       <c r="E263" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>11</v>
       </c>
@@ -8423,7 +8443,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>11</v>
       </c>
@@ -8431,16 +8451,16 @@
         <v>276</v>
       </c>
       <c r="C265">
-        <v>105.582</v>
+        <v>105.58199999999999</v>
       </c>
       <c r="D265">
-        <v>9.883419999999999</v>
+        <v>9.8834199999999992</v>
       </c>
       <c r="E265" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>11</v>
       </c>
@@ -8451,13 +8471,13 @@
         <v>105.65</v>
       </c>
       <c r="D266">
-        <v>9.875920000000001</v>
+        <v>9.8759200000000007</v>
       </c>
       <c r="E266" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>11</v>
       </c>
@@ -8465,16 +8485,16 @@
         <v>278</v>
       </c>
       <c r="C267">
-        <v>105.579</v>
+        <v>105.57899999999999</v>
       </c>
       <c r="D267">
-        <v>9.814450000000001</v>
+        <v>9.8144500000000008</v>
       </c>
       <c r="E267" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>11</v>
       </c>
@@ -8485,13 +8505,13 @@
         <v>105.649</v>
       </c>
       <c r="D268">
-        <v>9.811909999999999</v>
+        <v>9.8119099999999992</v>
       </c>
       <c r="E268" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>11</v>
       </c>
@@ -8499,16 +8519,16 @@
         <v>280</v>
       </c>
       <c r="C269">
-        <v>105.594</v>
+        <v>105.59399999999999</v>
       </c>
       <c r="D269">
-        <v>9.70825</v>
+        <v>9.7082499999999996</v>
       </c>
       <c r="E269" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>11</v>
       </c>
@@ -8519,13 +8539,13 @@
         <v>105.511</v>
       </c>
       <c r="D270">
-        <v>9.616989999999999</v>
+        <v>9.6169899999999995</v>
       </c>
       <c r="E270" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>11</v>
       </c>
@@ -8536,13 +8556,13 @@
         <v>105.675</v>
       </c>
       <c r="D271">
-        <v>9.69614</v>
+        <v>9.6961399999999998</v>
       </c>
       <c r="E271" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>11</v>
       </c>
@@ -8550,16 +8570,16 @@
         <v>283</v>
       </c>
       <c r="C272">
-        <v>105.716</v>
+        <v>105.71599999999999</v>
       </c>
       <c r="D272">
-        <v>9.73446</v>
+        <v>9.7344600000000003</v>
       </c>
       <c r="E272" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>11</v>
       </c>
@@ -8570,13 +8590,13 @@
         <v>105.63</v>
       </c>
       <c r="D273">
-        <v>9.69462</v>
+        <v>9.6946200000000005</v>
       </c>
       <c r="E273" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>11</v>
       </c>
@@ -8587,13 +8607,13 @@
         <v>105.55</v>
       </c>
       <c r="D274">
-        <v>9.654870000000001</v>
+        <v>9.6548700000000007</v>
       </c>
       <c r="E274" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>11</v>
       </c>
@@ -8604,13 +8624,13 @@
         <v>105.67</v>
       </c>
       <c r="D275">
-        <v>9.79039</v>
+        <v>9.7903900000000004</v>
       </c>
       <c r="E275" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>11</v>
       </c>
@@ -8627,7 +8647,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>11</v>
       </c>
@@ -8638,13 +8658,13 @@
         <v>105.464</v>
       </c>
       <c r="D277">
-        <v>9.78251</v>
+        <v>9.7825100000000003</v>
       </c>
       <c r="E277" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>11</v>
       </c>
@@ -8655,13 +8675,13 @@
         <v>105.688</v>
       </c>
       <c r="D278">
-        <v>9.67803</v>
+        <v>9.6780299999999997</v>
       </c>
       <c r="E278" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>11</v>
       </c>
@@ -8672,13 +8692,13 @@
         <v>105.64</v>
       </c>
       <c r="D279">
-        <v>9.7822</v>
+        <v>9.7821999999999996</v>
       </c>
       <c r="E279" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>11</v>
       </c>
@@ -8689,13 +8709,13 @@
         <v>105.501</v>
       </c>
       <c r="D280">
-        <v>9.772349999999999</v>
+        <v>9.7723499999999994</v>
       </c>
       <c r="E280" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>11</v>
       </c>
@@ -8712,7 +8732,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>11</v>
       </c>
@@ -8723,13 +8743,13 @@
         <v>105.518</v>
       </c>
       <c r="D282">
-        <v>9.80364</v>
+        <v>9.8036399999999997</v>
       </c>
       <c r="E282" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>11</v>
       </c>
@@ -8740,13 +8760,13 @@
         <v>105.654</v>
       </c>
       <c r="D283">
-        <v>9.66778</v>
+        <v>9.6677800000000005</v>
       </c>
       <c r="E283" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>11</v>
       </c>
@@ -8757,13 +8777,13 @@
         <v>105.669</v>
       </c>
       <c r="D284">
-        <v>9.89784</v>
+        <v>9.8978400000000004</v>
       </c>
       <c r="E284" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>11</v>
       </c>
@@ -8774,13 +8794,13 @@
         <v>105.498</v>
       </c>
       <c r="D285">
-        <v>9.763769999999999</v>
+        <v>9.7637699999999992</v>
       </c>
       <c r="E285" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>11</v>
       </c>
@@ -8788,16 +8808,16 @@
         <v>297</v>
       </c>
       <c r="C286">
-        <v>105.466</v>
+        <v>105.46599999999999</v>
       </c>
       <c r="D286">
-        <v>9.786490000000001</v>
+        <v>9.7864900000000006</v>
       </c>
       <c r="E286" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>11</v>
       </c>
@@ -8808,13 +8828,13 @@
         <v>105.577</v>
       </c>
       <c r="D287">
-        <v>9.682079999999999</v>
+        <v>9.6820799999999991</v>
       </c>
       <c r="E287" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>12</v>
       </c>
@@ -8822,7 +8842,7 @@
         <v>299</v>
       </c>
       <c r="C288">
-        <v>105.561</v>
+        <v>105.56100000000001</v>
       </c>
       <c r="D288">
         <v>10.6723</v>
@@ -8831,7 +8851,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>12</v>
       </c>
@@ -8842,13 +8862,13 @@
         <v>105.34</v>
       </c>
       <c r="D289">
-        <v>10.8092</v>
+        <v>10.809200000000001</v>
       </c>
       <c r="E289" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>12</v>
       </c>
@@ -8856,16 +8876,16 @@
         <v>301</v>
       </c>
       <c r="C290">
-        <v>105.472</v>
+        <v>105.47199999999999</v>
       </c>
       <c r="D290">
-        <v>10.8167</v>
+        <v>10.816700000000001</v>
       </c>
       <c r="E290" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>12</v>
       </c>
@@ -8882,7 +8902,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>12</v>
       </c>
@@ -8899,7 +8919,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>12</v>
       </c>
@@ -8910,13 +8930,13 @@
         <v>105.521</v>
       </c>
       <c r="D293">
-        <v>10.8211</v>
+        <v>10.821099999999999</v>
       </c>
       <c r="E293" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>12</v>
       </c>
@@ -8924,7 +8944,7 @@
         <v>305</v>
       </c>
       <c r="C294">
-        <v>105.522</v>
+        <v>105.52200000000001</v>
       </c>
       <c r="D294">
         <v>10.6214</v>
@@ -8933,7 +8953,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>12</v>
       </c>
@@ -8944,13 +8964,13 @@
         <v>105.416</v>
       </c>
       <c r="D295">
-        <v>10.6164</v>
+        <v>10.616400000000001</v>
       </c>
       <c r="E295" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>12</v>
       </c>
@@ -8967,7 +8987,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>12</v>
       </c>
@@ -8984,7 +9004,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>12</v>
       </c>
@@ -8995,13 +9015,13 @@
         <v>105.43</v>
       </c>
       <c r="D298">
-        <v>10.684</v>
+        <v>10.683999999999999</v>
       </c>
       <c r="E298" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>12</v>
       </c>
@@ -9012,13 +9032,13 @@
         <v>105.584</v>
       </c>
       <c r="D299">
-        <v>10.7916</v>
+        <v>10.791600000000001</v>
       </c>
       <c r="E299" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>12</v>
       </c>
@@ -9026,7 +9046,7 @@
         <v>311</v>
       </c>
       <c r="C300">
-        <v>105.513</v>
+        <v>105.51300000000001</v>
       </c>
       <c r="D300">
         <v>10.6106</v>
@@ -9035,7 +9055,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>12</v>
       </c>
@@ -9043,16 +9063,16 @@
         <v>312</v>
       </c>
       <c r="C301">
-        <v>105.418</v>
+        <v>105.41800000000001</v>
       </c>
       <c r="D301">
-        <v>10.6649</v>
+        <v>10.664899999999999</v>
       </c>
       <c r="E301" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>12</v>
       </c>
@@ -9060,7 +9080,7 @@
         <v>313</v>
       </c>
       <c r="C302">
-        <v>105.493</v>
+        <v>105.49299999999999</v>
       </c>
       <c r="D302">
         <v>10.5565</v>
@@ -9069,7 +9089,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>12</v>
       </c>
@@ -9080,13 +9100,13 @@
         <v>105.626</v>
       </c>
       <c r="D303">
-        <v>10.6711</v>
+        <v>10.671099999999999</v>
       </c>
       <c r="E303" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>12</v>
       </c>
@@ -9103,7 +9123,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>12</v>
       </c>
@@ -9120,7 +9140,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>12</v>
       </c>
@@ -9137,7 +9157,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>12</v>
       </c>
@@ -9154,7 +9174,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>12</v>
       </c>
@@ -9162,7 +9182,7 @@
         <v>319</v>
       </c>
       <c r="C308">
-        <v>105.528</v>
+        <v>105.52800000000001</v>
       </c>
       <c r="D308">
         <v>10.7416</v>
@@ -9171,7 +9191,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>12</v>
       </c>
@@ -9179,16 +9199,16 @@
         <v>320</v>
       </c>
       <c r="C309">
-        <v>105.484</v>
+        <v>105.48399999999999</v>
       </c>
       <c r="D309">
-        <v>10.8182</v>
+        <v>10.818199999999999</v>
       </c>
       <c r="E309" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>12</v>
       </c>
@@ -9199,13 +9219,13 @@
         <v>105.49</v>
       </c>
       <c r="D310">
-        <v>10.937</v>
+        <v>10.936999999999999</v>
       </c>
       <c r="E310" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>12</v>
       </c>
@@ -9213,7 +9233,7 @@
         <v>322</v>
       </c>
       <c r="C311">
-        <v>105.421</v>
+        <v>105.42100000000001</v>
       </c>
       <c r="D311">
         <v>10.6067</v>
@@ -9222,7 +9242,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>12</v>
       </c>
@@ -9239,7 +9259,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>12</v>
       </c>
@@ -9247,16 +9267,16 @@
         <v>324</v>
       </c>
       <c r="C313">
-        <v>105.201</v>
+        <v>105.20099999999999</v>
       </c>
       <c r="D313">
-        <v>10.9006</v>
+        <v>10.900600000000001</v>
       </c>
       <c r="E313" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>12</v>
       </c>
@@ -9264,16 +9284,16 @@
         <v>325</v>
       </c>
       <c r="C314">
-        <v>105.823</v>
+        <v>105.82299999999999</v>
       </c>
       <c r="D314">
-        <v>10.4418</v>
+        <v>10.441800000000001</v>
       </c>
       <c r="E314" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>12</v>
       </c>
@@ -9290,7 +9310,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>12</v>
       </c>
@@ -9307,7 +9327,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>12</v>
       </c>
@@ -9315,7 +9335,7 @@
         <v>328</v>
       </c>
       <c r="C317">
-        <v>105.847</v>
+        <v>105.84699999999999</v>
       </c>
       <c r="D317">
         <v>10.1982</v>
@@ -9324,7 +9344,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>12</v>
       </c>
@@ -9332,7 +9352,7 @@
         <v>329</v>
       </c>
       <c r="C318">
-        <v>105.716</v>
+        <v>105.71599999999999</v>
       </c>
       <c r="D318">
         <v>10.2133</v>
@@ -9341,7 +9361,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>12</v>
       </c>
@@ -9358,7 +9378,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>12</v>
       </c>
@@ -9366,16 +9386,16 @@
         <v>331</v>
       </c>
       <c r="C320">
-        <v>105.451</v>
+        <v>105.45099999999999</v>
       </c>
       <c r="D320">
-        <v>10.8816</v>
+        <v>10.881600000000001</v>
       </c>
       <c r="E320" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>12</v>
       </c>
@@ -9386,13 +9406,13 @@
         <v>105.6</v>
       </c>
       <c r="D321">
-        <v>10.3981</v>
+        <v>10.398099999999999</v>
       </c>
       <c r="E321" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>12</v>
       </c>
@@ -9409,7 +9429,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>12</v>
       </c>
@@ -9426,7 +9446,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>12</v>
       </c>
@@ -9437,13 +9457,13 @@
         <v>105.449</v>
       </c>
       <c r="D324">
-        <v>10.8793</v>
+        <v>10.879300000000001</v>
       </c>
       <c r="E324" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>12</v>
       </c>
@@ -9460,7 +9480,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>12</v>
       </c>
@@ -9468,7 +9488,7 @@
         <v>337</v>
       </c>
       <c r="C326">
-        <v>105.731</v>
+        <v>105.73099999999999</v>
       </c>
       <c r="D326">
         <v>10.3489</v>
@@ -9477,7 +9497,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>12</v>
       </c>
@@ -9485,7 +9505,7 @@
         <v>338</v>
       </c>
       <c r="C327">
-        <v>105.421</v>
+        <v>105.42100000000001</v>
       </c>
       <c r="D327">
         <v>10.6028</v>
@@ -9494,7 +9514,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>12</v>
       </c>
@@ -9511,7 +9531,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>12</v>
       </c>
@@ -9519,7 +9539,7 @@
         <v>340</v>
       </c>
       <c r="C329">
-        <v>105.865</v>
+        <v>105.86499999999999</v>
       </c>
       <c r="D329">
         <v>10.4955</v>
@@ -9528,7 +9548,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>12</v>
       </c>
@@ -9545,7 +9565,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>12</v>
       </c>
@@ -9562,7 +9582,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>12</v>
       </c>
@@ -9579,7 +9599,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>12</v>
       </c>
@@ -9587,7 +9607,7 @@
         <v>344</v>
       </c>
       <c r="C333">
-        <v>105.686</v>
+        <v>105.68600000000001</v>
       </c>
       <c r="D333">
         <v>10.5688</v>
@@ -9596,7 +9616,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>12</v>
       </c>
@@ -9607,13 +9627,13 @@
         <v>105.23</v>
       </c>
       <c r="D334">
-        <v>10.8221</v>
+        <v>10.822100000000001</v>
       </c>
       <c r="E334" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>12</v>
       </c>
@@ -9624,13 +9644,13 @@
         <v>105.75</v>
       </c>
       <c r="D335">
-        <v>10.4067</v>
+        <v>10.406700000000001</v>
       </c>
       <c r="E335" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>12</v>
       </c>
@@ -9641,13 +9661,13 @@
         <v>105.739</v>
       </c>
       <c r="D336">
-        <v>10.5277</v>
+        <v>10.527699999999999</v>
       </c>
       <c r="E336" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>12</v>
       </c>
@@ -9658,13 +9678,13 @@
         <v>105.812</v>
       </c>
       <c r="D337">
-        <v>10.5225</v>
+        <v>10.522500000000001</v>
       </c>
       <c r="E337" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>12</v>
       </c>
@@ -9681,7 +9701,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>12</v>
       </c>
@@ -9698,7 +9718,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>12</v>
       </c>
@@ -9715,7 +9735,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>12</v>
       </c>
@@ -9726,13 +9746,13 @@
         <v>105.27</v>
       </c>
       <c r="D341">
-        <v>10.889</v>
+        <v>10.888999999999999</v>
       </c>
       <c r="E341" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>12</v>
       </c>
@@ -9749,7 +9769,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>12</v>
       </c>
@@ -9757,16 +9777,16 @@
         <v>354</v>
       </c>
       <c r="C343">
-        <v>105.519</v>
+        <v>105.51900000000001</v>
       </c>
       <c r="D343">
-        <v>10.9135</v>
+        <v>10.913500000000001</v>
       </c>
       <c r="E343" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>12</v>
       </c>
@@ -9774,7 +9794,7 @@
         <v>355</v>
       </c>
       <c r="C344">
-        <v>105.359</v>
+        <v>105.35899999999999</v>
       </c>
       <c r="D344">
         <v>10.8172</v>
@@ -9783,7 +9803,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>12</v>
       </c>
@@ -9800,7 +9820,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>12</v>
       </c>
@@ -9811,13 +9831,13 @@
         <v>105.646</v>
       </c>
       <c r="D346">
-        <v>10.3838</v>
+        <v>10.383800000000001</v>
       </c>
       <c r="E346" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>12</v>
       </c>
@@ -9828,13 +9848,13 @@
         <v>105.495</v>
       </c>
       <c r="D347">
-        <v>10.5545</v>
+        <v>10.554500000000001</v>
       </c>
       <c r="E347" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>12</v>
       </c>
@@ -9845,13 +9865,13 @@
         <v>105.669</v>
       </c>
       <c r="D348">
-        <v>10.5666</v>
+        <v>10.566599999999999</v>
       </c>
       <c r="E348" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>12</v>
       </c>
@@ -9868,7 +9888,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>12</v>
       </c>
@@ -9879,13 +9899,13 @@
         <v>105.654</v>
       </c>
       <c r="D350">
-        <v>10.3272</v>
+        <v>10.327199999999999</v>
       </c>
       <c r="E350" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>12</v>
       </c>
@@ -9896,13 +9916,13 @@
         <v>105.854</v>
       </c>
       <c r="D351">
-        <v>10.4661</v>
+        <v>10.466100000000001</v>
       </c>
       <c r="E351" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>12</v>
       </c>
@@ -9913,13 +9933,13 @@
         <v>105.813</v>
       </c>
       <c r="D352">
-        <v>10.1863</v>
+        <v>10.186299999999999</v>
       </c>
       <c r="E352" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>12</v>
       </c>
@@ -9936,7 +9956,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>12</v>
       </c>
@@ -9953,7 +9973,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>12</v>
       </c>
@@ -9961,16 +9981,16 @@
         <v>366</v>
       </c>
       <c r="C355">
-        <v>105.731</v>
+        <v>105.73099999999999</v>
       </c>
       <c r="D355">
-        <v>10.7048</v>
+        <v>10.704800000000001</v>
       </c>
       <c r="E355" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>12</v>
       </c>
@@ -9987,7 +10007,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>12</v>
       </c>
@@ -10004,7 +10024,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>12</v>
       </c>
@@ -10012,7 +10032,7 @@
         <v>369</v>
       </c>
       <c r="C358">
-        <v>105.728</v>
+        <v>105.72799999999999</v>
       </c>
       <c r="D358">
         <v>10.6007</v>
@@ -10021,7 +10041,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>12</v>
       </c>
@@ -10029,7 +10049,7 @@
         <v>370</v>
       </c>
       <c r="C359">
-        <v>105.222</v>
+        <v>105.22199999999999</v>
       </c>
       <c r="D359">
         <v>10.8459</v>
@@ -10038,7 +10058,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>12</v>
       </c>
@@ -10055,7 +10075,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>12</v>
       </c>
@@ -10063,16 +10083,16 @@
         <v>372</v>
       </c>
       <c r="C361">
-        <v>105.618</v>
+        <v>105.61799999999999</v>
       </c>
       <c r="D361">
-        <v>10.4898</v>
+        <v>10.489800000000001</v>
       </c>
       <c r="E361" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>12</v>
       </c>
@@ -10089,7 +10109,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>12</v>
       </c>
@@ -10097,7 +10117,7 @@
         <v>374</v>
       </c>
       <c r="C363">
-        <v>105.859</v>
+        <v>105.85899999999999</v>
       </c>
       <c r="D363">
         <v>10.4077</v>
@@ -10106,7 +10126,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>12</v>
       </c>
@@ -10123,7 +10143,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>12</v>
       </c>
@@ -10140,7 +10160,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>12</v>
       </c>
@@ -10157,7 +10177,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>12</v>
       </c>
@@ -10165,16 +10185,16 @@
         <v>377</v>
       </c>
       <c r="C367">
-        <v>105.305</v>
+        <v>105.30500000000001</v>
       </c>
       <c r="D367">
-        <v>10.7543</v>
+        <v>10.754300000000001</v>
       </c>
       <c r="E367" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>12</v>
       </c>
@@ -10185,13 +10205,13 @@
         <v>105.669</v>
       </c>
       <c r="D368">
-        <v>10.6437</v>
+        <v>10.643700000000001</v>
       </c>
       <c r="E368" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>12</v>
       </c>
@@ -10202,13 +10222,13 @@
         <v>105.74</v>
       </c>
       <c r="D369">
-        <v>10.4684</v>
+        <v>10.468400000000001</v>
       </c>
       <c r="E369" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>12</v>
       </c>
@@ -10219,13 +10239,13 @@
         <v>105.691</v>
       </c>
       <c r="D370">
-        <v>10.7252</v>
+        <v>10.725199999999999</v>
       </c>
       <c r="E370" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>7</v>
       </c>
@@ -10236,13 +10256,13 @@
         <v>105.524</v>
       </c>
       <c r="D371">
-        <v>10.2436</v>
+        <v>10.243600000000001</v>
       </c>
       <c r="E371" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>12</v>
       </c>
@@ -10253,13 +10273,13 @@
         <v>105.63</v>
       </c>
       <c r="D372">
-        <v>10.607</v>
+        <v>10.606999999999999</v>
       </c>
       <c r="E372" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>7</v>
       </c>
@@ -10270,13 +10290,13 @@
         <v>105.529</v>
       </c>
       <c r="D373">
-        <v>10.2754</v>
+        <v>10.275399999999999</v>
       </c>
       <c r="E373" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>7</v>
       </c>
@@ -10287,13 +10307,13 @@
         <v>105.43</v>
       </c>
       <c r="D374">
-        <v>10.095</v>
+        <v>10.095000000000001</v>
       </c>
       <c r="E374" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>7</v>
       </c>
@@ -10301,7 +10321,7 @@
         <v>385</v>
       </c>
       <c r="C375">
-        <v>105.558</v>
+        <v>105.55800000000001</v>
       </c>
       <c r="D375">
         <v>10.0303</v>
@@ -10310,7 +10330,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>7</v>
       </c>
@@ -10318,16 +10338,16 @@
         <v>386</v>
       </c>
       <c r="C376">
-        <v>105.344</v>
+        <v>105.34399999999999</v>
       </c>
       <c r="D376">
-        <v>10.1779</v>
+        <v>10.177899999999999</v>
       </c>
       <c r="E376" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>7</v>
       </c>
@@ -10344,7 +10364,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>7</v>
       </c>
@@ -10361,7 +10381,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>7</v>
       </c>
@@ -10378,7 +10398,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>7</v>
       </c>
@@ -10395,7 +10415,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>7</v>
       </c>
@@ -10406,13 +10426,13 @@
         <v>105.464</v>
       </c>
       <c r="D381">
-        <v>10.1551</v>
+        <v>10.155099999999999</v>
       </c>
       <c r="E381" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>7</v>
       </c>
@@ -10429,7 +10449,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>7</v>
       </c>
@@ -10446,7 +10466,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>7</v>
       </c>
@@ -10457,13 +10477,13 @@
         <v>105.438</v>
       </c>
       <c r="D384">
-        <v>10.2045</v>
+        <v>10.204499999999999</v>
       </c>
       <c r="E384" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>7</v>
       </c>
@@ -10474,13 +10494,13 @@
         <v>105.413</v>
       </c>
       <c r="D385">
-        <v>10.1702</v>
+        <v>10.170199999999999</v>
       </c>
       <c r="E385" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>7</v>
       </c>
@@ -10497,7 +10517,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>7</v>
       </c>
@@ -10508,13 +10528,13 @@
         <v>105.42</v>
       </c>
       <c r="D387">
-        <v>10.079</v>
+        <v>10.079000000000001</v>
       </c>
       <c r="E387" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>7</v>
       </c>
@@ -10525,13 +10545,13 @@
         <v>105.258</v>
       </c>
       <c r="D388">
-        <v>10.2083</v>
+        <v>10.208299999999999</v>
       </c>
       <c r="E388" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>7</v>
       </c>
@@ -10548,7 +10568,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>7</v>
       </c>
@@ -10559,13 +10579,13 @@
         <v>105.553</v>
       </c>
       <c r="D390">
-        <v>10.2292</v>
+        <v>10.229200000000001</v>
       </c>
       <c r="E390" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>7</v>
       </c>
@@ -10582,7 +10602,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>7</v>
       </c>
@@ -10593,13 +10613,13 @@
         <v>105.545</v>
       </c>
       <c r="D392">
-        <v>10.0681</v>
+        <v>10.068099999999999</v>
       </c>
       <c r="E392" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>7</v>
       </c>
@@ -10610,13 +10630,13 @@
         <v>105.435</v>
       </c>
       <c r="D393">
-        <v>10.1582</v>
+        <v>10.158200000000001</v>
       </c>
       <c r="E393" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>7</v>
       </c>
@@ -10627,13 +10647,13 @@
         <v>105.485</v>
       </c>
       <c r="D394">
-        <v>10.2985</v>
+        <v>10.298500000000001</v>
       </c>
       <c r="E394" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>7</v>
       </c>
@@ -10650,7 +10670,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>7</v>
       </c>
@@ -10661,13 +10681,13 @@
         <v>105.43</v>
       </c>
       <c r="D396">
-        <v>10.0934</v>
+        <v>10.093400000000001</v>
       </c>
       <c r="E396" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>7</v>
       </c>
@@ -10678,13 +10698,13 @@
         <v>105.505</v>
       </c>
       <c r="D397">
-        <v>10.2053</v>
+        <v>10.205299999999999</v>
       </c>
       <c r="E397" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>7</v>
       </c>
@@ -10695,13 +10715,13 @@
         <v>105.477</v>
       </c>
       <c r="D398">
-        <v>10.1781</v>
+        <v>10.178100000000001</v>
       </c>
       <c r="E398" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>7</v>
       </c>
@@ -10718,7 +10738,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>7</v>
       </c>
@@ -10729,13 +10749,13 @@
         <v>105.587</v>
       </c>
       <c r="D400">
-        <v>10.0851</v>
+        <v>10.085100000000001</v>
       </c>
       <c r="E400" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>7</v>
       </c>
@@ -10743,7 +10763,7 @@
         <v>409</v>
       </c>
       <c r="C401">
-        <v>105.382</v>
+        <v>105.38200000000001</v>
       </c>
       <c r="D401">
         <v>10.0794</v>
@@ -10752,7 +10772,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>7</v>
       </c>
@@ -10760,16 +10780,16 @@
         <v>410</v>
       </c>
       <c r="C402">
-        <v>105.341</v>
+        <v>105.34099999999999</v>
       </c>
       <c r="D402">
-        <v>10.2269</v>
+        <v>10.226900000000001</v>
       </c>
       <c r="E402" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>7</v>
       </c>
@@ -10777,7 +10797,7 @@
         <v>411</v>
       </c>
       <c r="C403">
-        <v>105.344</v>
+        <v>105.34399999999999</v>
       </c>
       <c r="D403">
         <v>10.1777</v>
@@ -10786,7 +10806,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>7</v>
       </c>
@@ -10794,7 +10814,7 @@
         <v>412</v>
       </c>
       <c r="C404">
-        <v>105.534</v>
+        <v>105.53400000000001</v>
       </c>
       <c r="D404">
         <v>10.0054</v>
@@ -10803,7 +10823,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>13</v>
       </c>
@@ -10814,13 +10834,13 @@
         <v>105.617</v>
       </c>
       <c r="D405">
-        <v>9.292529999999999</v>
+        <v>9.2925299999999993</v>
       </c>
       <c r="E405" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>13</v>
       </c>
@@ -10831,13 +10851,13 @@
         <v>105.49</v>
       </c>
       <c r="D406">
-        <v>9.36009</v>
+        <v>9.3600899999999996</v>
       </c>
       <c r="E406" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>13</v>
       </c>
@@ -10848,13 +10868,13 @@
         <v>104.887</v>
       </c>
       <c r="D407">
-        <v>9.177379999999999</v>
+        <v>9.1773799999999994</v>
       </c>
       <c r="E407" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>13</v>
       </c>
@@ -10865,13 +10885,13 @@
         <v>105.129</v>
       </c>
       <c r="D408">
-        <v>9.207509999999999</v>
+        <v>9.2075099999999992</v>
       </c>
       <c r="E408" t="s">
         <v>981</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>13</v>
       </c>
@@ -10888,7 +10908,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>13</v>
       </c>
@@ -10899,13 +10919,13 @@
         <v>105.011</v>
       </c>
       <c r="D410">
-        <v>9.15189</v>
+        <v>9.1518899999999999</v>
       </c>
       <c r="E410" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>13</v>
       </c>
@@ -10913,16 +10933,16 @@
         <v>419</v>
       </c>
       <c r="C411">
-        <v>105.897</v>
+        <v>105.89700000000001</v>
       </c>
       <c r="D411">
-        <v>9.70757</v>
+        <v>9.7075700000000005</v>
       </c>
       <c r="E411" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>13</v>
       </c>
@@ -10930,16 +10950,16 @@
         <v>420</v>
       </c>
       <c r="C412">
-        <v>105.862</v>
+        <v>105.86199999999999</v>
       </c>
       <c r="D412">
-        <v>9.67526</v>
+        <v>9.6752599999999997</v>
       </c>
       <c r="E412" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>13</v>
       </c>
@@ -10950,13 +10970,13 @@
         <v>105.84</v>
       </c>
       <c r="D413">
-        <v>9.658390000000001</v>
+        <v>9.6583900000000007</v>
       </c>
       <c r="E413" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>13</v>
       </c>
@@ -10973,7 +10993,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>13</v>
       </c>
@@ -10984,13 +11004,13 @@
         <v>105.96</v>
       </c>
       <c r="D415">
-        <v>9.6881</v>
+        <v>9.6881000000000004</v>
       </c>
       <c r="E415" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>13</v>
       </c>
@@ -10998,16 +11018,16 @@
         <v>424</v>
       </c>
       <c r="C416">
-        <v>105.799</v>
+        <v>105.79900000000001</v>
       </c>
       <c r="D416">
-        <v>9.675979999999999</v>
+        <v>9.6759799999999991</v>
       </c>
       <c r="E416" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>13</v>
       </c>
@@ -11018,13 +11038,13 @@
         <v>105.509</v>
       </c>
       <c r="D417">
-        <v>9.397220000000001</v>
+        <v>9.3972200000000008</v>
       </c>
       <c r="E417" t="s">
         <v>990</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>13</v>
       </c>
@@ -11035,13 +11055,13 @@
         <v>105.58</v>
       </c>
       <c r="D418">
-        <v>9.47001</v>
+        <v>9.4700100000000003</v>
       </c>
       <c r="E418" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>13</v>
       </c>
@@ -11049,16 +11069,16 @@
         <v>427</v>
       </c>
       <c r="C419">
-        <v>105.659</v>
+        <v>105.65900000000001</v>
       </c>
       <c r="D419">
-        <v>9.635210000000001</v>
+        <v>9.6352100000000007</v>
       </c>
       <c r="E419" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>13</v>
       </c>
@@ -11069,13 +11089,13 @@
         <v>105.569</v>
       </c>
       <c r="D420">
-        <v>9.540089999999999</v>
+        <v>9.5400899999999993</v>
       </c>
       <c r="E420" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>13</v>
       </c>
@@ -11086,13 +11106,13 @@
         <v>105.693</v>
       </c>
       <c r="D421">
-        <v>9.418950000000001</v>
+        <v>9.4189500000000006</v>
       </c>
       <c r="E421" t="s">
         <v>993</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>13</v>
       </c>
@@ -11100,16 +11120,16 @@
         <v>430</v>
       </c>
       <c r="C422">
-        <v>105.421</v>
+        <v>105.42100000000001</v>
       </c>
       <c r="D422">
-        <v>9.589320000000001</v>
+        <v>9.5893200000000007</v>
       </c>
       <c r="E422" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>13</v>
       </c>
@@ -11117,16 +11137,16 @@
         <v>431</v>
       </c>
       <c r="C423">
-        <v>105.597</v>
+        <v>105.59699999999999</v>
       </c>
       <c r="D423">
-        <v>9.486219999999999</v>
+        <v>9.4862199999999994</v>
       </c>
       <c r="E423" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>13</v>
       </c>
@@ -11143,7 +11163,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>13</v>
       </c>
@@ -11151,16 +11171,16 @@
         <v>433</v>
       </c>
       <c r="C425">
-        <v>105.713</v>
+        <v>105.71299999999999</v>
       </c>
       <c r="D425">
-        <v>9.38571</v>
+        <v>9.3857099999999996</v>
       </c>
       <c r="E425" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>13</v>
       </c>
@@ -11168,16 +11188,16 @@
         <v>434</v>
       </c>
       <c r="C426">
-        <v>105.647</v>
+        <v>105.64700000000001</v>
       </c>
       <c r="D426">
-        <v>9.613289999999999</v>
+        <v>9.6132899999999992</v>
       </c>
       <c r="E426" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>13</v>
       </c>
@@ -11188,13 +11208,13 @@
         <v>105.685</v>
       </c>
       <c r="D427">
-        <v>9.29792</v>
+        <v>9.2979199999999995</v>
       </c>
       <c r="E427" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>13</v>
       </c>
@@ -11205,13 +11225,13 @@
         <v>105.578</v>
       </c>
       <c r="D428">
-        <v>9.44387</v>
+        <v>9.4438700000000004</v>
       </c>
       <c r="E428" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>13</v>
       </c>
@@ -11222,13 +11242,13 @@
         <v>105.899</v>
       </c>
       <c r="D429">
-        <v>9.706670000000001</v>
+        <v>9.7066700000000008</v>
       </c>
       <c r="E429" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>13</v>
       </c>
@@ -11239,13 +11259,13 @@
         <v>105.836</v>
       </c>
       <c r="D430">
-        <v>9.654339999999999</v>
+        <v>9.6543399999999995</v>
       </c>
       <c r="E430" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>13</v>
       </c>
@@ -11253,33 +11273,33 @@
         <v>439</v>
       </c>
       <c r="C431">
-        <v>105.603</v>
+        <v>105.60299999999999</v>
       </c>
       <c r="D431">
-        <v>9.53755</v>
+        <v>9.5375499999999995</v>
       </c>
       <c r="E431" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B432" t="s">
         <v>440</v>
       </c>
       <c r="C432">
-        <v>105.772</v>
+        <v>105.77200000000001</v>
       </c>
       <c r="D432">
-        <v>10.0264</v>
+        <v>10.026400000000001</v>
       </c>
       <c r="E432" t="s">
         <v>1003</v>
       </c>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>13</v>
       </c>
@@ -11290,13 +11310,13 @@
         <v>105.73</v>
       </c>
       <c r="D433">
-        <v>9.5435</v>
+        <v>9.5434999999999999</v>
       </c>
       <c r="E433" t="s">
         <v>1004</v>
       </c>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>13</v>
       </c>
@@ -11307,13 +11327,13 @@
         <v>106.083</v>
       </c>
       <c r="D434">
-        <v>9.50539</v>
+        <v>9.5053900000000002</v>
       </c>
       <c r="E434" t="s">
         <v>1005</v>
       </c>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>13</v>
       </c>
@@ -11324,13 +11344,13 @@
         <v>106.008</v>
       </c>
       <c r="D435">
-        <v>9.466659999999999</v>
+        <v>9.4666599999999992</v>
       </c>
       <c r="E435" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>13</v>
       </c>
@@ -11341,13 +11361,13 @@
         <v>105.99</v>
       </c>
       <c r="D436">
-        <v>9.5558</v>
+        <v>9.5557999999999996</v>
       </c>
       <c r="E436" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>13</v>
       </c>
@@ -11355,7 +11375,7 @@
         <v>445</v>
       </c>
       <c r="C437">
-        <v>106.025</v>
+        <v>106.02500000000001</v>
       </c>
       <c r="D437">
         <v>9.54209</v>
@@ -11364,7 +11384,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>13</v>
       </c>
@@ -11375,13 +11395,13 @@
         <v>106.12</v>
       </c>
       <c r="D438">
-        <v>9.532439999999999</v>
+        <v>9.5324399999999994</v>
       </c>
       <c r="E438" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>13</v>
       </c>
@@ -11392,13 +11412,13 @@
         <v>106.14</v>
       </c>
       <c r="D439">
-        <v>9.48882</v>
+        <v>9.4888200000000005</v>
       </c>
       <c r="E439" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>13</v>
       </c>
@@ -11409,13 +11429,13 @@
         <v>106.033</v>
       </c>
       <c r="D440">
-        <v>9.716670000000001</v>
+        <v>9.7166700000000006</v>
       </c>
       <c r="E440" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>13</v>
       </c>
@@ -11426,13 +11446,13 @@
         <v>105.982</v>
       </c>
       <c r="D441">
-        <v>9.52524</v>
+        <v>9.5252400000000002</v>
       </c>
       <c r="E441" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>13</v>
       </c>
@@ -11443,13 +11463,13 @@
         <v>105.479</v>
       </c>
       <c r="D442">
-        <v>9.29726</v>
+        <v>9.2972599999999996</v>
       </c>
       <c r="E442" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>13</v>
       </c>
@@ -11460,13 +11480,13 @@
         <v>105.72</v>
       </c>
       <c r="D443">
-        <v>9.4611</v>
+        <v>9.4611000000000001</v>
       </c>
       <c r="E443" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>13</v>
       </c>
@@ -11477,13 +11497,13 @@
         <v>105.6</v>
       </c>
       <c r="D444">
-        <v>9.3894</v>
+        <v>9.3894000000000002</v>
       </c>
       <c r="E444" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>13</v>
       </c>
@@ -11494,13 +11514,13 @@
         <v>105.599</v>
       </c>
       <c r="D445">
-        <v>9.390079999999999</v>
+        <v>9.3900799999999993</v>
       </c>
       <c r="E445" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>13</v>
       </c>
@@ -11511,13 +11531,13 @@
         <v>105.631</v>
       </c>
       <c r="D446">
-        <v>9.450810000000001</v>
+        <v>9.4508100000000006</v>
       </c>
       <c r="E446" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>13</v>
       </c>
@@ -11528,13 +11548,13 @@
         <v>106.035</v>
       </c>
       <c r="D447">
-        <v>9.62247</v>
+        <v>9.6224699999999999</v>
       </c>
       <c r="E447" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>13</v>
       </c>
@@ -11542,16 +11562,16 @@
         <v>456</v>
       </c>
       <c r="C448">
-        <v>106.112</v>
+        <v>106.11199999999999</v>
       </c>
       <c r="D448">
-        <v>9.35202</v>
+        <v>9.3520199999999996</v>
       </c>
       <c r="E448" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>13</v>
       </c>
@@ -11562,13 +11582,13 @@
         <v>106.054</v>
       </c>
       <c r="D449">
-        <v>9.701269999999999</v>
+        <v>9.7012699999999992</v>
       </c>
       <c r="E449" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>13</v>
       </c>
@@ -11585,7 +11605,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>13</v>
       </c>
@@ -11596,13 +11616,13 @@
         <v>105.965</v>
       </c>
       <c r="D451">
-        <v>9.70818</v>
+        <v>9.7081800000000005</v>
       </c>
       <c r="E451" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>13</v>
       </c>
@@ -11613,13 +11633,13 @@
         <v>105.694</v>
       </c>
       <c r="D452">
-        <v>9.297129999999999</v>
+        <v>9.2971299999999992</v>
       </c>
       <c r="E452" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>13</v>
       </c>
@@ -11636,7 +11656,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>13</v>
       </c>
@@ -11644,16 +11664,16 @@
         <v>379</v>
       </c>
       <c r="C454">
-        <v>105.713</v>
+        <v>105.71299999999999</v>
       </c>
       <c r="D454">
-        <v>9.385429999999999</v>
+        <v>9.3854299999999995</v>
       </c>
       <c r="E454" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>13</v>
       </c>
@@ -11661,16 +11681,16 @@
         <v>462</v>
       </c>
       <c r="C455">
-        <v>105.906</v>
+        <v>105.90600000000001</v>
       </c>
       <c r="D455">
-        <v>9.597289999999999</v>
+        <v>9.5972899999999992</v>
       </c>
       <c r="E455" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>13</v>
       </c>
@@ -11681,13 +11701,13 @@
         <v>106.125</v>
       </c>
       <c r="D456">
-        <v>9.60342</v>
+        <v>9.6034199999999998</v>
       </c>
       <c r="E456" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>13</v>
       </c>
@@ -11695,7 +11715,7 @@
         <v>464</v>
       </c>
       <c r="C457">
-        <v>105.853</v>
+        <v>105.85299999999999</v>
       </c>
       <c r="D457">
         <v>9.71706</v>
@@ -11704,7 +11724,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>13</v>
       </c>
@@ -11715,13 +11735,13 @@
         <v>105.872</v>
       </c>
       <c r="D458">
-        <v>9.739750000000001</v>
+        <v>9.7397500000000008</v>
       </c>
       <c r="E458" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>13</v>
       </c>
@@ -11729,16 +11749,16 @@
         <v>466</v>
       </c>
       <c r="C459">
-        <v>105.853</v>
+        <v>105.85299999999999</v>
       </c>
       <c r="D459">
-        <v>9.71429</v>
+        <v>9.7142900000000001</v>
       </c>
       <c r="E459" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>13</v>
       </c>
@@ -11746,16 +11766,16 @@
         <v>467</v>
       </c>
       <c r="C460">
-        <v>105.853</v>
+        <v>105.85299999999999</v>
       </c>
       <c r="D460">
-        <v>9.720789999999999</v>
+        <v>9.7207899999999992</v>
       </c>
       <c r="E460" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>13</v>
       </c>
@@ -11766,13 +11786,13 @@
         <v>106.127</v>
       </c>
       <c r="D461">
-        <v>9.606490000000001</v>
+        <v>9.6064900000000009</v>
       </c>
       <c r="E461" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>13</v>
       </c>
@@ -11783,13 +11803,13 @@
         <v>105.724</v>
       </c>
       <c r="D462">
-        <v>9.45262</v>
+        <v>9.4526199999999996</v>
       </c>
       <c r="E462" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>13</v>
       </c>
@@ -11797,7 +11817,7 @@
         <v>470</v>
       </c>
       <c r="C463">
-        <v>105.692</v>
+        <v>105.69199999999999</v>
       </c>
       <c r="D463">
         <v>9.42103</v>
@@ -11806,7 +11826,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>13</v>
       </c>
@@ -11817,13 +11837,13 @@
         <v>105.91</v>
       </c>
       <c r="D464">
-        <v>9.6012</v>
+        <v>9.6012000000000004</v>
       </c>
       <c r="E464" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>13</v>
       </c>
@@ -11834,13 +11854,13 @@
         <v>105.911</v>
       </c>
       <c r="D465">
-        <v>9.60127</v>
+        <v>9.6012699999999995</v>
       </c>
       <c r="E465" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>13</v>
       </c>
@@ -11848,16 +11868,16 @@
         <v>473</v>
       </c>
       <c r="C466">
-        <v>106.007</v>
+        <v>106.00700000000001</v>
       </c>
       <c r="D466">
-        <v>9.326930000000001</v>
+        <v>9.3269300000000008</v>
       </c>
       <c r="E466" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>13</v>
       </c>
@@ -11868,13 +11888,13 @@
         <v>106.131</v>
       </c>
       <c r="D467">
-        <v>9.57164</v>
+        <v>9.5716400000000004</v>
       </c>
       <c r="E467" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>13</v>
       </c>
@@ -11885,13 +11905,13 @@
         <v>105.935</v>
       </c>
       <c r="D468">
-        <v>9.54965</v>
+        <v>9.5496499999999997</v>
       </c>
       <c r="E468" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>13</v>
       </c>
@@ -11902,13 +11922,13 @@
         <v>106.12</v>
       </c>
       <c r="D469">
-        <v>9.490309999999999</v>
+        <v>9.4903099999999991</v>
       </c>
       <c r="E469" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>13</v>
       </c>
@@ -11919,13 +11939,13 @@
         <v>105.89</v>
       </c>
       <c r="D470">
-        <v>9.71593</v>
+        <v>9.7159300000000002</v>
       </c>
       <c r="E470" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>13</v>
       </c>
@@ -11936,13 +11956,13 @@
         <v>105.92</v>
       </c>
       <c r="D471">
-        <v>9.630850000000001</v>
+        <v>9.6308500000000006</v>
       </c>
       <c r="E471" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>13</v>
       </c>
@@ -11953,13 +11973,13 @@
         <v>105.456</v>
       </c>
       <c r="D472">
-        <v>9.307840000000001</v>
+        <v>9.3078400000000006</v>
       </c>
       <c r="E472" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="473" spans="1:5">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>14</v>
       </c>
@@ -11970,13 +11990,13 @@
         <v>105.232</v>
       </c>
       <c r="D473">
-        <v>10.5811</v>
+        <v>10.581099999999999</v>
       </c>
       <c r="E473" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="474" spans="1:5">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>13</v>
       </c>
@@ -11987,13 +12007,13 @@
         <v>105.883</v>
       </c>
       <c r="D474">
-        <v>9.661530000000001</v>
+        <v>9.6615300000000008</v>
       </c>
       <c r="E474" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="475" spans="1:5">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>14</v>
       </c>
@@ -12004,13 +12024,13 @@
         <v>104.89</v>
       </c>
       <c r="D475">
-        <v>10.495</v>
+        <v>10.494999999999999</v>
       </c>
       <c r="E475" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="476" spans="1:5">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>14</v>
       </c>
@@ -12021,13 +12041,13 @@
         <v>105.129</v>
       </c>
       <c r="D476">
-        <v>10.7192</v>
+        <v>10.719200000000001</v>
       </c>
       <c r="E476" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="477" spans="1:5">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>13</v>
       </c>
@@ -12035,16 +12055,16 @@
         <v>484</v>
       </c>
       <c r="C477">
-        <v>105.743</v>
+        <v>105.74299999999999</v>
       </c>
       <c r="D477">
-        <v>9.68871</v>
+        <v>9.6887100000000004</v>
       </c>
       <c r="E477" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="478" spans="1:5">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>14</v>
       </c>
@@ -12061,7 +12081,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="479" spans="1:5">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>14</v>
       </c>
@@ -12072,13 +12092,13 @@
         <v>105.17</v>
       </c>
       <c r="D479">
-        <v>10.4425</v>
+        <v>10.442500000000001</v>
       </c>
       <c r="E479" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="480" spans="1:5">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>14</v>
       </c>
@@ -12089,13 +12109,13 @@
         <v>105.17</v>
       </c>
       <c r="D480">
-        <v>10.4402</v>
+        <v>10.440200000000001</v>
       </c>
       <c r="E480" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="481" spans="1:5">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>14</v>
       </c>
@@ -12106,13 +12126,13 @@
         <v>105.127</v>
       </c>
       <c r="D481">
-        <v>10.6604</v>
+        <v>10.660399999999999</v>
       </c>
       <c r="E481" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="482" spans="1:5">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>14</v>
       </c>
@@ -12120,7 +12140,7 @@
         <v>489</v>
       </c>
       <c r="C482">
-        <v>105.481</v>
+        <v>105.48099999999999</v>
       </c>
       <c r="D482">
         <v>10.3695</v>
@@ -12129,7 +12149,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="483" spans="1:5">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>14</v>
       </c>
@@ -12140,13 +12160,13 @@
         <v>105.262</v>
       </c>
       <c r="D483">
-        <v>10.6626</v>
+        <v>10.662599999999999</v>
       </c>
       <c r="E483" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="484" spans="1:5">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>14</v>
       </c>
@@ -12157,13 +12177,13 @@
         <v>105.191</v>
       </c>
       <c r="D484">
-        <v>10.7983</v>
+        <v>10.798299999999999</v>
       </c>
       <c r="E484" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="485" spans="1:5">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>14</v>
       </c>
@@ -12174,13 +12194,13 @@
         <v>105.501</v>
       </c>
       <c r="D485">
-        <v>10.4005</v>
+        <v>10.400499999999999</v>
       </c>
       <c r="E485" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="486" spans="1:5">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>14</v>
       </c>
@@ -12191,13 +12211,13 @@
         <v>105.407</v>
       </c>
       <c r="D486">
-        <v>10.3715</v>
+        <v>10.371499999999999</v>
       </c>
       <c r="E486" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="487" spans="1:5">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>14</v>
       </c>
@@ -12208,13 +12228,13 @@
         <v>105.28</v>
       </c>
       <c r="D487">
-        <v>10.361</v>
+        <v>10.361000000000001</v>
       </c>
       <c r="E487" t="s">
         <v>1049</v>
       </c>
     </row>
-    <row r="488" spans="1:5">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>14</v>
       </c>
@@ -12231,7 +12251,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="489" spans="1:5">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>14</v>
       </c>
@@ -12248,7 +12268,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="490" spans="1:5">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>14</v>
       </c>
@@ -12265,7 +12285,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>14</v>
       </c>
@@ -12273,16 +12293,16 @@
         <v>498</v>
       </c>
       <c r="C491">
-        <v>105.147</v>
+        <v>105.14700000000001</v>
       </c>
       <c r="D491">
-        <v>10.3321</v>
+        <v>10.332100000000001</v>
       </c>
       <c r="E491" t="s">
         <v>1053</v>
       </c>
     </row>
-    <row r="492" spans="1:5">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>14</v>
       </c>
@@ -12290,7 +12310,7 @@
         <v>499</v>
       </c>
       <c r="C492">
-        <v>105.368</v>
+        <v>105.36799999999999</v>
       </c>
       <c r="D492">
         <v>10.3559</v>
@@ -12299,7 +12319,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="493" spans="1:5">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>14</v>
       </c>
@@ -12310,13 +12330,13 @@
         <v>105.148</v>
       </c>
       <c r="D493">
-        <v>10.3319</v>
+        <v>10.331899999999999</v>
       </c>
       <c r="E493" t="s">
         <v>1055</v>
       </c>
     </row>
-    <row r="494" spans="1:5">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>14</v>
       </c>
@@ -12327,13 +12347,13 @@
         <v>105.407</v>
       </c>
       <c r="D494">
-        <v>10.3715</v>
+        <v>10.371499999999999</v>
       </c>
       <c r="E494" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>14</v>
       </c>
@@ -12350,7 +12370,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>14</v>
       </c>
@@ -12358,7 +12378,7 @@
         <v>503</v>
       </c>
       <c r="C496">
-        <v>105.305</v>
+        <v>105.30500000000001</v>
       </c>
       <c r="D496">
         <v>10.5738</v>
@@ -12367,7 +12387,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="497" spans="1:5">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>14</v>
       </c>
@@ -12378,13 +12398,13 @@
         <v>105.083</v>
       </c>
       <c r="D497">
-        <v>10.7998</v>
+        <v>10.799799999999999</v>
       </c>
       <c r="E497" t="s">
         <v>1058</v>
       </c>
     </row>
-    <row r="498" spans="1:5">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>14</v>
       </c>
@@ -12401,7 +12421,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="499" spans="1:5">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>14</v>
       </c>
@@ -12418,7 +12438,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="500" spans="1:5">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>14</v>
       </c>
@@ -12435,7 +12455,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="501" spans="1:5">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>14</v>
       </c>
@@ -12446,13 +12466,13 @@
         <v>105.172</v>
       </c>
       <c r="D501">
-        <v>10.6391</v>
+        <v>10.639099999999999</v>
       </c>
       <c r="E501" t="s">
         <v>1062</v>
       </c>
     </row>
-    <row r="502" spans="1:5">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>14</v>
       </c>
@@ -12469,7 +12489,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>14</v>
       </c>
@@ -12477,16 +12497,16 @@
         <v>510</v>
       </c>
       <c r="C503">
-        <v>105.049</v>
+        <v>105.04900000000001</v>
       </c>
       <c r="D503">
-        <v>10.8693</v>
+        <v>10.869300000000001</v>
       </c>
       <c r="E503" t="s">
         <v>1064</v>
       </c>
     </row>
-    <row r="504" spans="1:5">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>14</v>
       </c>
@@ -12497,13 +12517,13 @@
         <v>105.273</v>
       </c>
       <c r="D504">
-        <v>10.5553</v>
+        <v>10.555300000000001</v>
       </c>
       <c r="E504" t="s">
         <v>1065</v>
       </c>
     </row>
-    <row r="505" spans="1:5">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>14</v>
       </c>
@@ -12514,13 +12534,13 @@
         <v>105.126</v>
       </c>
       <c r="D505">
-        <v>10.8982</v>
+        <v>10.898199999999999</v>
       </c>
       <c r="E505" t="s">
         <v>1066</v>
       </c>
     </row>
-    <row r="506" spans="1:5">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>14</v>
       </c>
@@ -12528,7 +12548,7 @@
         <v>513</v>
       </c>
       <c r="C506">
-        <v>105.091</v>
+        <v>105.09099999999999</v>
       </c>
       <c r="D506">
         <v>10.8169</v>
@@ -12537,7 +12557,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="507" spans="1:5">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>14</v>
       </c>
@@ -12548,13 +12568,13 @@
         <v>105.527</v>
       </c>
       <c r="D507">
-        <v>10.4981</v>
+        <v>10.498100000000001</v>
       </c>
       <c r="E507" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="508" spans="1:5">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>14</v>
       </c>
@@ -12571,7 +12591,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="509" spans="1:5">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>14</v>
       </c>
@@ -12588,7 +12608,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="510" spans="1:5">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>14</v>
       </c>
@@ -12596,7 +12616,7 @@
         <v>517</v>
       </c>
       <c r="C510">
-        <v>105.335</v>
+        <v>105.33499999999999</v>
       </c>
       <c r="D510">
         <v>10.6724</v>
@@ -12605,7 +12625,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="511" spans="1:5">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>14</v>
       </c>
@@ -12613,7 +12633,7 @@
         <v>518</v>
       </c>
       <c r="C511">
-        <v>105.162</v>
+        <v>105.16200000000001</v>
       </c>
       <c r="D511">
         <v>10.7807</v>
@@ -12622,7 +12642,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="512" spans="1:5">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>14</v>
       </c>
@@ -12639,7 +12659,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>14</v>
       </c>
@@ -12650,13 +12670,13 @@
         <v>105.246</v>
       </c>
       <c r="D513">
-        <v>10.7413</v>
+        <v>10.741300000000001</v>
       </c>
       <c r="E513" t="s">
         <v>1074</v>
       </c>
     </row>
-    <row r="514" spans="1:5">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>14</v>
       </c>
@@ -12667,13 +12687,13 @@
         <v>105.029</v>
       </c>
       <c r="D514">
-        <v>10.6141</v>
+        <v>10.614100000000001</v>
       </c>
       <c r="E514" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="515" spans="1:5">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>14</v>
       </c>
@@ -12690,7 +12710,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="516" spans="1:5">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>14</v>
       </c>
@@ -12707,7 +12727,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="517" spans="1:5">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>14</v>
       </c>
@@ -12715,16 +12735,16 @@
         <v>524</v>
       </c>
       <c r="C517">
-        <v>104.993</v>
+        <v>104.99299999999999</v>
       </c>
       <c r="D517">
-        <v>10.5513</v>
+        <v>10.551299999999999</v>
       </c>
       <c r="E517" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="518" spans="1:5">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>14</v>
       </c>
@@ -12732,16 +12752,16 @@
         <v>525</v>
       </c>
       <c r="C518">
-        <v>105.186</v>
+        <v>105.18600000000001</v>
       </c>
       <c r="D518">
-        <v>10.5455</v>
+        <v>10.545500000000001</v>
       </c>
       <c r="E518" t="s">
         <v>1056</v>
       </c>
     </row>
-    <row r="519" spans="1:5">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>14</v>
       </c>
@@ -12749,16 +12769,16 @@
         <v>526</v>
       </c>
       <c r="C519">
-        <v>104.903</v>
+        <v>104.90300000000001</v>
       </c>
       <c r="D519">
-        <v>10.4966</v>
+        <v>10.496600000000001</v>
       </c>
       <c r="E519" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="520" spans="1:5">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>14</v>
       </c>
@@ -12775,7 +12795,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="521" spans="1:5">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>14</v>
       </c>
@@ -12783,7 +12803,7 @@
         <v>528</v>
       </c>
       <c r="C521">
-        <v>105.216</v>
+        <v>105.21599999999999</v>
       </c>
       <c r="D521">
         <v>10.7521</v>
@@ -12792,7 +12812,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>14</v>
       </c>
@@ -12809,7 +12829,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="523" spans="1:5">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>14</v>
       </c>
@@ -12826,7 +12846,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="524" spans="1:5">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>14</v>
       </c>
@@ -12837,13 +12857,13 @@
         <v>105.01</v>
       </c>
       <c r="D524">
-        <v>10.547</v>
+        <v>10.547000000000001</v>
       </c>
       <c r="E524" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="525" spans="1:5">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>14</v>
       </c>
@@ -12854,13 +12874,13 @@
         <v>105.084</v>
       </c>
       <c r="D525">
-        <v>10.9547</v>
+        <v>10.954700000000001</v>
       </c>
       <c r="E525" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="526" spans="1:5">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>14</v>
       </c>
@@ -12871,13 +12891,13 @@
         <v>105.148</v>
       </c>
       <c r="D526">
-        <v>10.2587</v>
+        <v>10.258699999999999</v>
       </c>
       <c r="E526" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="527" spans="1:5">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>14</v>
       </c>
@@ -12888,13 +12908,13 @@
         <v>105.035</v>
       </c>
       <c r="D527">
-        <v>10.5156</v>
+        <v>10.515599999999999</v>
       </c>
       <c r="E527" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="528" spans="1:5">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>14</v>
       </c>
@@ -12911,7 +12931,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>14</v>
       </c>
@@ -12928,7 +12948,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="530" spans="1:5">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>14</v>
       </c>
@@ -12939,13 +12959,13 @@
         <v>105.02</v>
       </c>
       <c r="D530">
-        <v>10.483</v>
+        <v>10.483000000000001</v>
       </c>
       <c r="E530" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="531" spans="1:5">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>14</v>
       </c>
@@ -12962,7 +12982,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="532" spans="1:5">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>14</v>
       </c>
@@ -12979,7 +12999,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="533" spans="1:5">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>14</v>
       </c>
@@ -12987,16 +13007,16 @@
         <v>540</v>
       </c>
       <c r="C533">
-        <v>105.082</v>
+        <v>105.08199999999999</v>
       </c>
       <c r="D533">
-        <v>10.9525</v>
+        <v>10.952500000000001</v>
       </c>
       <c r="E533" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>14</v>
       </c>
@@ -13004,7 +13024,7 @@
         <v>541</v>
       </c>
       <c r="C534">
-        <v>105.243</v>
+        <v>105.24299999999999</v>
       </c>
       <c r="D534">
         <v>10.2615</v>
@@ -13013,7 +13033,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>14</v>
       </c>
@@ -13030,7 +13050,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="536" spans="1:5">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>14</v>
       </c>
@@ -13047,7 +13067,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="537" spans="1:5">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>14</v>
       </c>
@@ -13058,13 +13078,13 @@
         <v>105</v>
       </c>
       <c r="D537">
-        <v>10.428</v>
+        <v>10.428000000000001</v>
       </c>
       <c r="E537" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>14</v>
       </c>
@@ -13075,13 +13095,13 @@
         <v>105.03</v>
       </c>
       <c r="D538">
-        <v>10.517</v>
+        <v>10.516999999999999</v>
       </c>
       <c r="E538" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="539" spans="1:5">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>14</v>
       </c>
@@ -13098,7 +13118,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="540" spans="1:5">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>14</v>
       </c>
@@ -13115,7 +13135,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>14</v>
       </c>
@@ -13132,7 +13152,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="542" spans="1:5">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>14</v>
       </c>
@@ -13149,7 +13169,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="543" spans="1:5">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>14</v>
       </c>
@@ -13166,7 +13186,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="544" spans="1:5">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>14</v>
       </c>
@@ -13183,7 +13203,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="545" spans="1:5">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>14</v>
       </c>
@@ -13191,16 +13211,16 @@
         <v>552</v>
       </c>
       <c r="C545">
-        <v>105.079</v>
+        <v>105.07899999999999</v>
       </c>
       <c r="D545">
-        <v>10.8554</v>
+        <v>10.855399999999999</v>
       </c>
       <c r="E545" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="546" spans="1:5">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>14</v>
       </c>
@@ -13217,7 +13237,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>14</v>
       </c>
@@ -13225,16 +13245,16 @@
         <v>554</v>
       </c>
       <c r="C547">
-        <v>105.365</v>
+        <v>105.36499999999999</v>
       </c>
       <c r="D547">
-        <v>10.3235</v>
+        <v>10.323499999999999</v>
       </c>
       <c r="E547" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>14</v>
       </c>
@@ -13245,13 +13265,13 @@
         <v>105.235</v>
       </c>
       <c r="D548">
-        <v>10.4067</v>
+        <v>10.406700000000001</v>
       </c>
       <c r="E548" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>9</v>
       </c>
@@ -13259,7 +13279,7 @@
         <v>556</v>
       </c>
       <c r="C549">
-        <v>107.573</v>
+        <v>107.57299999999999</v>
       </c>
       <c r="D549">
         <v>11.1869</v>
@@ -13268,7 +13288,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>9</v>
       </c>
@@ -13285,7 +13305,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>9</v>
       </c>
@@ -13293,7 +13313,7 @@
         <v>558</v>
       </c>
       <c r="C551">
-        <v>108.421</v>
+        <v>108.42100000000001</v>
       </c>
       <c r="D551">
         <v>11.2171</v>
@@ -13302,7 +13322,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>9</v>
       </c>
@@ -13319,7 +13339,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>9</v>
       </c>
@@ -13327,16 +13347,16 @@
         <v>560</v>
       </c>
       <c r="C553">
-        <v>108.281</v>
+        <v>108.28100000000001</v>
       </c>
       <c r="D553">
-        <v>11.1987</v>
+        <v>11.198700000000001</v>
       </c>
       <c r="E553" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>9</v>
       </c>
@@ -13344,7 +13364,7 @@
         <v>561</v>
       </c>
       <c r="C554">
-        <v>108.132</v>
+        <v>108.13200000000001</v>
       </c>
       <c r="D554">
         <v>11.1052</v>
@@ -13353,7 +13373,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>9</v>
       </c>
@@ -13370,7 +13390,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>9</v>
       </c>
@@ -13387,7 +13407,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>9</v>
       </c>
@@ -13398,13 +13418,13 @@
         <v>108.214</v>
       </c>
       <c r="D557">
-        <v>11.1733</v>
+        <v>11.173299999999999</v>
       </c>
       <c r="E557" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>9</v>
       </c>
@@ -13421,7 +13441,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="559" spans="1:5">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>9</v>
       </c>
@@ -13432,13 +13452,13 @@
         <v>108.163</v>
       </c>
       <c r="D559">
-        <v>11.0301</v>
+        <v>11.030099999999999</v>
       </c>
       <c r="E559" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="560" spans="1:5">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>9</v>
       </c>
@@ -13455,7 +13475,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="561" spans="1:5">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>9</v>
       </c>
@@ -13466,13 +13486,13 @@
         <v>108.496</v>
       </c>
       <c r="D561">
-        <v>11.2282</v>
+        <v>11.228199999999999</v>
       </c>
       <c r="E561" t="s">
         <v>1111</v>
       </c>
     </row>
-    <row r="562" spans="1:5">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>9</v>
       </c>
@@ -13489,7 +13509,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>9</v>
       </c>
@@ -13506,7 +13526,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="564" spans="1:5">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>9</v>
       </c>
@@ -13523,7 +13543,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>9</v>
       </c>
@@ -13540,7 +13560,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="566" spans="1:5">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>9</v>
       </c>
@@ -13551,13 +13571,13 @@
         <v>107.312</v>
       </c>
       <c r="D566">
-        <v>10.9408</v>
+        <v>10.940799999999999</v>
       </c>
       <c r="E566" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>9</v>
       </c>
@@ -13574,7 +13594,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="568" spans="1:5">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>9</v>
       </c>
@@ -13591,7 +13611,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="569" spans="1:5">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>9</v>
       </c>
@@ -13608,7 +13628,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>9</v>
       </c>
@@ -13625,7 +13645,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="571" spans="1:5">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>9</v>
       </c>
@@ -13642,7 +13662,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="572" spans="1:5">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>9</v>
       </c>
@@ -13653,13 +13673,13 @@
         <v>107.533</v>
       </c>
       <c r="D572">
-        <v>11.3838</v>
+        <v>11.383800000000001</v>
       </c>
       <c r="E572" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>9</v>
       </c>
@@ -13676,7 +13696,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="574" spans="1:5">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>9</v>
       </c>
@@ -13687,13 +13707,13 @@
         <v>107.628</v>
       </c>
       <c r="D574">
-        <v>11.1461</v>
+        <v>11.146100000000001</v>
       </c>
       <c r="E574" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="575" spans="1:5">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>9</v>
       </c>
@@ -13710,7 +13730,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="576" spans="1:5">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>9</v>
       </c>
@@ -13721,13 +13741,13 @@
         <v>107.504</v>
       </c>
       <c r="D576">
-        <v>11.2894</v>
+        <v>11.289400000000001</v>
       </c>
       <c r="E576" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="577" spans="1:5">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>9</v>
       </c>
@@ -13738,13 +13758,13 @@
         <v>107.627</v>
       </c>
       <c r="D577">
-        <v>11.4098</v>
+        <v>11.409800000000001</v>
       </c>
       <c r="E577" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="578" spans="1:5">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>9</v>
       </c>
@@ -13752,16 +13772,16 @@
         <v>584</v>
       </c>
       <c r="C578">
-        <v>107.493</v>
+        <v>107.49299999999999</v>
       </c>
       <c r="D578">
-        <v>11.1458</v>
+        <v>11.145799999999999</v>
       </c>
       <c r="E578" t="s">
         <v>1128</v>
       </c>
     </row>
-    <row r="579" spans="1:5">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>9</v>
       </c>
@@ -13778,7 +13798,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="580" spans="1:5">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>9</v>
       </c>
@@ -13795,7 +13815,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="581" spans="1:5">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>9</v>
       </c>
@@ -13803,16 +13823,16 @@
         <v>587</v>
       </c>
       <c r="C581">
-        <v>107.088</v>
+        <v>107.08799999999999</v>
       </c>
       <c r="D581">
-        <v>10.9868</v>
+        <v>10.986800000000001</v>
       </c>
       <c r="E581" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="582" spans="1:5">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>9</v>
       </c>
@@ -13829,7 +13849,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="583" spans="1:5">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>9</v>
       </c>
@@ -13846,7 +13866,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="584" spans="1:5">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>9</v>
       </c>
@@ -13857,13 +13877,13 @@
         <v>108.18</v>
       </c>
       <c r="D584">
-        <v>11.751</v>
+        <v>11.750999999999999</v>
       </c>
       <c r="E584" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="585" spans="1:5">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>9</v>
       </c>
@@ -13871,16 +13891,16 @@
         <v>591</v>
       </c>
       <c r="C585">
-        <v>108.257</v>
+        <v>108.25700000000001</v>
       </c>
       <c r="D585">
-        <v>11.7731</v>
+        <v>11.773099999999999</v>
       </c>
       <c r="E585" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="586" spans="1:5">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>9</v>
       </c>
@@ -13888,7 +13908,7 @@
         <v>592</v>
       </c>
       <c r="C586">
-        <v>108.603</v>
+        <v>108.60299999999999</v>
       </c>
       <c r="D586">
         <v>11.8446</v>
@@ -13897,7 +13917,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="587" spans="1:5">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>9</v>
       </c>
@@ -13905,16 +13925,16 @@
         <v>593</v>
       </c>
       <c r="C587">
-        <v>108.213</v>
+        <v>108.21299999999999</v>
       </c>
       <c r="D587">
-        <v>11.6156</v>
+        <v>11.615600000000001</v>
       </c>
       <c r="E587" t="s">
         <v>1137</v>
       </c>
     </row>
-    <row r="588" spans="1:5">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>9</v>
       </c>
@@ -13925,13 +13945,13 @@
         <v>108.515</v>
       </c>
       <c r="D588">
-        <v>11.9426</v>
+        <v>11.942600000000001</v>
       </c>
       <c r="E588" t="s">
         <v>1138</v>
       </c>
     </row>
-    <row r="589" spans="1:5">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>9</v>
       </c>
@@ -13942,13 +13962,13 @@
         <v>108.479</v>
       </c>
       <c r="D589">
-        <v>11.7603</v>
+        <v>11.760300000000001</v>
       </c>
       <c r="E589" t="s">
         <v>1139</v>
       </c>
     </row>
-    <row r="590" spans="1:5">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>9</v>
       </c>
@@ -13965,7 +13985,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="591" spans="1:5">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>9</v>
       </c>
@@ -13976,13 +13996,13 @@
         <v>108.37</v>
       </c>
       <c r="D591">
-        <v>11.7046</v>
+        <v>11.704599999999999</v>
       </c>
       <c r="E591" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="592" spans="1:5">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>9</v>
       </c>
@@ -13993,13 +14013,13 @@
         <v>108.42</v>
       </c>
       <c r="D592">
-        <v>11.9768</v>
+        <v>11.976800000000001</v>
       </c>
       <c r="E592" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="593" spans="1:5">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>9</v>
       </c>
@@ -14007,16 +14027,16 @@
         <v>599</v>
       </c>
       <c r="C593">
-        <v>108.546</v>
+        <v>108.54600000000001</v>
       </c>
       <c r="D593">
-        <v>11.7969</v>
+        <v>11.796900000000001</v>
       </c>
       <c r="E593" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="594" spans="1:5">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>9</v>
       </c>
@@ -14027,13 +14047,13 @@
         <v>108.441</v>
       </c>
       <c r="D594">
-        <v>11.9729</v>
+        <v>11.972899999999999</v>
       </c>
       <c r="E594" t="s">
         <v>1144</v>
       </c>
     </row>
-    <row r="595" spans="1:5">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>9</v>
       </c>
@@ -14041,7 +14061,7 @@
         <v>601</v>
       </c>
       <c r="C595">
-        <v>108.579</v>
+        <v>108.57899999999999</v>
       </c>
       <c r="D595">
         <v>11.8055</v>
@@ -14050,7 +14070,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="596" spans="1:5">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>9</v>
       </c>
@@ -14067,7 +14087,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="597" spans="1:5">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>9</v>
       </c>
@@ -14075,16 +14095,16 @@
         <v>603</v>
       </c>
       <c r="C597">
-        <v>108.368</v>
+        <v>108.36799999999999</v>
       </c>
       <c r="D597">
-        <v>11.7054</v>
+        <v>11.705399999999999</v>
       </c>
       <c r="E597" t="s">
         <v>1147</v>
       </c>
     </row>
-    <row r="598" spans="1:5">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>9</v>
       </c>
@@ -14092,16 +14112,16 @@
         <v>604</v>
       </c>
       <c r="C598">
-        <v>108.427</v>
+        <v>108.42700000000001</v>
       </c>
       <c r="D598">
-        <v>11.7793</v>
+        <v>11.779299999999999</v>
       </c>
       <c r="E598" t="s">
         <v>1148</v>
       </c>
     </row>
-    <row r="599" spans="1:5">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>9</v>
       </c>
@@ -14109,16 +14129,16 @@
         <v>605</v>
       </c>
       <c r="C599">
-        <v>108.415</v>
+        <v>108.41500000000001</v>
       </c>
       <c r="D599">
-        <v>12.0019</v>
+        <v>12.001899999999999</v>
       </c>
       <c r="E599" t="s">
         <v>1149</v>
       </c>
     </row>
-    <row r="600" spans="1:5">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>9</v>
       </c>
@@ -14129,13 +14149,13 @@
         <v>108.453</v>
       </c>
       <c r="D600">
-        <v>11.9653</v>
+        <v>11.965299999999999</v>
       </c>
       <c r="E600" t="s">
         <v>1150</v>
       </c>
     </row>
-    <row r="601" spans="1:5">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>9</v>
       </c>
@@ -14152,7 +14172,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="602" spans="1:5">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>9</v>
       </c>
@@ -14160,16 +14180,16 @@
         <v>608</v>
       </c>
       <c r="C602">
-        <v>108.493</v>
+        <v>108.49299999999999</v>
       </c>
       <c r="D602">
-        <v>11.9448</v>
+        <v>11.944800000000001</v>
       </c>
       <c r="E602" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="603" spans="1:5">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>9</v>
       </c>
@@ -14180,13 +14200,13 @@
         <v>108.36</v>
       </c>
       <c r="D603">
-        <v>11.717</v>
+        <v>11.717000000000001</v>
       </c>
       <c r="E603" t="s">
         <v>1153</v>
       </c>
     </row>
-    <row r="604" spans="1:5">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>9</v>
       </c>
@@ -14197,13 +14217,13 @@
         <v>108.221</v>
       </c>
       <c r="D604">
-        <v>11.6184</v>
+        <v>11.618399999999999</v>
       </c>
       <c r="E604" t="s">
         <v>1137</v>
       </c>
     </row>
-    <row r="605" spans="1:5">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>9</v>
       </c>
@@ -14214,13 +14234,13 @@
         <v>108.194</v>
       </c>
       <c r="D605">
-        <v>11.7474</v>
+        <v>11.747400000000001</v>
       </c>
       <c r="E605" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="606" spans="1:5">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>9</v>
       </c>
@@ -14228,16 +14248,16 @@
         <v>612</v>
       </c>
       <c r="C606">
-        <v>108.415</v>
+        <v>108.41500000000001</v>
       </c>
       <c r="D606">
-        <v>12.0072</v>
+        <v>12.007199999999999</v>
       </c>
       <c r="E606" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="607" spans="1:5">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>9</v>
       </c>
@@ -14254,7 +14274,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="608" spans="1:5">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>9</v>
       </c>
@@ -14265,13 +14285,13 @@
         <v>108.452</v>
       </c>
       <c r="D608">
-        <v>11.9639</v>
+        <v>11.963900000000001</v>
       </c>
       <c r="E608" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="609" spans="1:5">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>9</v>
       </c>
@@ -14288,7 +14308,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="610" spans="1:5">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>9</v>
       </c>
@@ -14296,7 +14316,7 @@
         <v>616</v>
       </c>
       <c r="C610">
-        <v>108.308</v>
+        <v>108.30800000000001</v>
       </c>
       <c r="D610">
         <v>11.6943</v>
@@ -14305,7 +14325,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="611" spans="1:5">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>9</v>
       </c>
@@ -14316,13 +14336,13 @@
         <v>108.453</v>
       </c>
       <c r="D611">
-        <v>11.9654</v>
+        <v>11.965400000000001</v>
       </c>
       <c r="E611" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="612" spans="1:5">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>9</v>
       </c>
@@ -14330,16 +14350,16 @@
         <v>618</v>
       </c>
       <c r="C612">
-        <v>108.424</v>
+        <v>108.42400000000001</v>
       </c>
       <c r="D612">
-        <v>11.7566</v>
+        <v>11.756600000000001</v>
       </c>
       <c r="E612" t="s">
         <v>1161</v>
       </c>
     </row>
-    <row r="613" spans="1:5">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>9</v>
       </c>
@@ -14347,16 +14367,16 @@
         <v>619</v>
       </c>
       <c r="C613">
-        <v>108.475</v>
+        <v>108.47499999999999</v>
       </c>
       <c r="D613">
-        <v>11.9669</v>
+        <v>11.966900000000001</v>
       </c>
       <c r="E613" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="614" spans="1:5">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>9</v>
       </c>
@@ -14373,7 +14393,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="615" spans="1:5">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>9</v>
       </c>
@@ -14390,7 +14410,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="616" spans="1:5">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>9</v>
       </c>
@@ -14398,16 +14418,16 @@
         <v>622</v>
       </c>
       <c r="C616">
-        <v>106.049</v>
+        <v>106.04900000000001</v>
       </c>
       <c r="D616">
-        <v>11.3699</v>
+        <v>11.369899999999999</v>
       </c>
       <c r="E616" t="s">
         <v>1164</v>
       </c>
     </row>
-    <row r="617" spans="1:5">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>9</v>
       </c>
@@ -14415,7 +14435,7 @@
         <v>623</v>
       </c>
       <c r="C617">
-        <v>106.132</v>
+        <v>106.13200000000001</v>
       </c>
       <c r="D617">
         <v>11.3127</v>
@@ -14424,7 +14444,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="618" spans="1:5">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>9</v>
       </c>
@@ -14432,7 +14452,7 @@
         <v>624</v>
       </c>
       <c r="C618">
-        <v>106.231</v>
+        <v>106.23099999999999</v>
       </c>
       <c r="D618">
         <v>11.0839</v>
@@ -14441,7 +14461,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="619" spans="1:5">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>9</v>
       </c>
@@ -14452,13 +14472,13 @@
         <v>106.318</v>
       </c>
       <c r="D619">
-        <v>11.0606</v>
+        <v>11.060600000000001</v>
       </c>
       <c r="E619" t="s">
         <v>1167</v>
       </c>
     </row>
-    <row r="620" spans="1:5">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>9</v>
       </c>
@@ -14475,7 +14495,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="621" spans="1:5">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>9</v>
       </c>
@@ -14492,7 +14512,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="622" spans="1:5">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>9</v>
       </c>
@@ -14509,7 +14529,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="623" spans="1:5">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>9</v>
       </c>
@@ -14520,13 +14540,13 @@
         <v>106.084</v>
       </c>
       <c r="D623">
-        <v>11.2886</v>
+        <v>11.288600000000001</v>
       </c>
       <c r="E623" t="s">
         <v>1171</v>
       </c>
     </row>
-    <row r="624" spans="1:5">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>9</v>
       </c>
@@ -14543,7 +14563,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="625" spans="1:5">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>9</v>
       </c>
@@ -14560,7 +14580,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="626" spans="1:5">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>9</v>
       </c>
@@ -14571,13 +14591,13 @@
         <v>106.134</v>
       </c>
       <c r="D626">
-        <v>11.1215</v>
+        <v>11.121499999999999</v>
       </c>
       <c r="E626" t="s">
         <v>1174</v>
       </c>
     </row>
-    <row r="627" spans="1:5">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>9</v>
       </c>
@@ -14588,13 +14608,13 @@
         <v>106.114</v>
       </c>
       <c r="D627">
-        <v>11.4494</v>
+        <v>11.449400000000001</v>
       </c>
       <c r="E627" t="s">
         <v>1175</v>
       </c>
     </row>
-    <row r="628" spans="1:5">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>9</v>
       </c>
@@ -14605,13 +14625,13 @@
         <v>106.232</v>
       </c>
       <c r="D628">
-        <v>11.0833</v>
+        <v>11.083299999999999</v>
       </c>
       <c r="E628" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="629" spans="1:5">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>9</v>
       </c>
@@ -14628,7 +14648,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="630" spans="1:5">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>9</v>
       </c>
@@ -14645,7 +14665,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="631" spans="1:5">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>9</v>
       </c>
@@ -14662,7 +14682,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="632" spans="1:5">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>9</v>
       </c>
@@ -14673,13 +14693,13 @@
         <v>106.279</v>
       </c>
       <c r="D632">
-        <v>11.0751</v>
+        <v>11.075100000000001</v>
       </c>
       <c r="E632" t="s">
         <v>1179</v>
       </c>
     </row>
-    <row r="633" spans="1:5">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>9</v>
       </c>
@@ -14696,7 +14716,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="634" spans="1:5">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>9</v>
       </c>
@@ -14713,7 +14733,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="635" spans="1:5">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>9</v>
       </c>
@@ -14724,13 +14744,13 @@
         <v>106.209</v>
       </c>
       <c r="D635">
-        <v>11.1702</v>
+        <v>11.170199999999999</v>
       </c>
       <c r="E635" t="s">
         <v>1182</v>
       </c>
     </row>
-    <row r="636" spans="1:5">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>9</v>
       </c>
@@ -14741,13 +14761,13 @@
         <v>107.383</v>
       </c>
       <c r="D636">
-        <v>10.5658</v>
+        <v>10.565799999999999</v>
       </c>
       <c r="E636" t="s">
         <v>1183</v>
       </c>
     </row>
-    <row r="637" spans="1:5">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>9</v>
       </c>
@@ -14755,7 +14775,7 @@
         <v>643</v>
       </c>
       <c r="C637">
-        <v>106.228</v>
+        <v>106.22799999999999</v>
       </c>
       <c r="D637">
         <v>11.0379</v>
@@ -14764,7 +14784,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="638" spans="1:5">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>9</v>
       </c>
@@ -14772,7 +14792,7 @@
         <v>644</v>
       </c>
       <c r="C638">
-        <v>107.231</v>
+        <v>107.23099999999999</v>
       </c>
       <c r="D638">
         <v>10.4857</v>
@@ -14781,7 +14801,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="639" spans="1:5">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>9</v>
       </c>
